--- a/datos/2025-11-06-ejemplo-std-tecnico.xlsx
+++ b/datos/2025-11-06-ejemplo-std-tecnico.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="815" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{892CE2A7-FF39-4AD3-A8F6-B262DF5A63B9}"/>
+  <xr:revisionPtr revIDLastSave="819" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B5BBDD-EBB7-4467-9734-177531AE2285}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="975" windowWidth="15390" windowHeight="14250" tabRatio="675" activeTab="1" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
   <sheets>
     <sheet name="Estándar de fab" sheetId="21" r:id="rId1"/>
@@ -4008,10 +4008,10 @@
         <v>70</v>
       </c>
       <c r="C1" s="79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="79" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="79" t="s">
-        <v>7</v>
       </c>
       <c r="E1" s="79" t="s">
         <v>8</v>
@@ -4054,10 +4054,10 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3">
+        <v>0.55630000000000002</v>
+      </c>
+      <c r="D4" s="3">
         <v>0.54949999999999999</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.55630000000000002</v>
       </c>
       <c r="E4" s="3">
         <v>0.5635</v>
@@ -4072,10 +4072,10 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4">
+        <v>0.30049999999999999</v>
+      </c>
+      <c r="D5" s="4">
         <v>0.30280000000000001</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.30049999999999999</v>
       </c>
       <c r="E5" s="4">
         <v>0.30930000000000002</v>
@@ -4093,14 +4093,14 @@
       </c>
       <c r="C6" s="14">
         <f>C4-C5</f>
+        <v>0.25580000000000003</v>
+      </c>
+      <c r="D6" s="14">
+        <f>D4-D5</f>
         <v>0.24669999999999997</v>
       </c>
-      <c r="D6" s="14">
-        <f t="shared" ref="D6:F6" si="0">D4-D5</f>
-        <v>0.25580000000000003</v>
-      </c>
       <c r="E6" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E6:F6" si="0">E4-E5</f>
         <v>0.25419999999999998</v>
       </c>
       <c r="F6" s="14">
@@ -4117,14 +4117,14 @@
       </c>
       <c r="C7" s="16">
         <f>(1-C4)/(1-C5)</f>
+        <v>0.63431022158684769</v>
+      </c>
+      <c r="D7" s="16">
+        <f>(1-D4)/(1-D5)</f>
         <v>0.64615605278255883</v>
       </c>
-      <c r="D7" s="16">
-        <f t="shared" ref="D7:F7" si="1">(1-D4)/(1-D5)</f>
-        <v>0.63431022158684769</v>
-      </c>
       <c r="E7" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E7:F7" si="1">(1-E4)/(1-E5)</f>
         <v>0.63196756913276386</v>
       </c>
       <c r="F7" s="16">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C8" s="18">
         <f>C5/C4</f>
+        <v>0.54017616394031998</v>
+      </c>
+      <c r="D8" s="18">
+        <f>D5/D4</f>
         <v>0.55104640582347597</v>
       </c>
-      <c r="D8" s="18">
-        <f t="shared" ref="D8:F8" si="2">D5/D4</f>
-        <v>0.54017616394031998</v>
-      </c>
       <c r="E8" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E8:F8" si="2">E5/E4</f>
         <v>0.54889086069210291</v>
       </c>
       <c r="F8" s="18">
@@ -4172,10 +4172,10 @@
       </c>
       <c r="B10" s="91"/>
       <c r="C10" s="91">
+        <v>40.1</v>
+      </c>
+      <c r="D10" s="91">
         <v>41.37</v>
-      </c>
-      <c r="D10" s="91">
-        <v>38.89</v>
       </c>
       <c r="E10" s="91">
         <v>71.05</v>
@@ -4190,10 +4190,10 @@
       </c>
       <c r="B11" s="93"/>
       <c r="C11" s="93">
+        <v>33.5</v>
+      </c>
+      <c r="D11" s="93">
         <v>32.049999999999997</v>
-      </c>
-      <c r="D11" s="93">
-        <v>31.77</v>
       </c>
       <c r="E11" s="93">
         <v>56.97</v>
@@ -4218,10 +4218,10 @@
       </c>
       <c r="B13" s="97"/>
       <c r="C13" s="97">
+        <v>0.92498000000000002</v>
+      </c>
+      <c r="D13" s="97">
         <v>0.96779999999999999</v>
-      </c>
-      <c r="D13" s="97">
-        <v>0.95279999999999998</v>
       </c>
       <c r="E13" s="97">
         <v>0.93479999999999996</v>
@@ -4249,11 +4249,11 @@
       </c>
       <c r="C15" s="21">
         <f>C13*C11</f>
-        <v>31.017989999999998</v>
+        <v>30.986830000000001</v>
       </c>
       <c r="D15" s="21">
         <f>D13*D11</f>
-        <v>30.270455999999999</v>
+        <v>31.017989999999998</v>
       </c>
       <c r="E15" s="21">
         <f>E13*E11</f>
@@ -4273,11 +4273,11 @@
       </c>
       <c r="C16" s="80">
         <f>C6*1000/C15</f>
-        <v>7.9534489501092756</v>
+        <v>8.2551199977538854</v>
       </c>
       <c r="D16" s="80">
         <f>D6*1000/D15</f>
-        <v>8.4504838645311473</v>
+        <v>7.9534489501092756</v>
       </c>
       <c r="E16" s="80">
         <f>E6*1000/E15</f>
@@ -4297,11 +4297,11 @@
       </c>
       <c r="C17" s="21">
         <f>C5*1000/C16</f>
-        <v>38.071533733279288</v>
+        <v>36.401651348709926</v>
       </c>
       <c r="D17" s="21">
         <f>D5*1000/D16</f>
-        <v>35.560093932759962</v>
+        <v>38.071533733279288</v>
       </c>
       <c r="E17" s="21">
         <f>E5*1000/E16</f>
@@ -4321,14 +4321,14 @@
       </c>
       <c r="C18" s="78">
         <f>C17/C10</f>
+        <v>0.9077718540825418</v>
+      </c>
+      <c r="D18" s="78">
+        <f>D17/D10</f>
         <v>0.92026912577421538</v>
       </c>
-      <c r="D18" s="78">
-        <f t="shared" ref="D18:F18" si="3">D17/D10</f>
-        <v>0.91437629037695967</v>
-      </c>
       <c r="E18" s="78">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E18:F18" si="3">E17/E10</f>
         <v>0.91202179019772545</v>
       </c>
       <c r="F18" s="78">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="C19" s="74">
         <f>C17-C10</f>
+        <v>-3.6983486512900754</v>
+      </c>
+      <c r="D19" s="74">
+        <f>D17-D10</f>
         <v>-3.298466266720709</v>
       </c>
-      <c r="D19" s="74">
-        <f t="shared" ref="D19:F19" si="4">D17-D10</f>
-        <v>-3.3299060672400387</v>
-      </c>
       <c r="E19" s="74">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E19:F19" si="4">E17-E10</f>
         <v>-6.2508518064516068</v>
       </c>
       <c r="F19" s="74">
@@ -4369,14 +4369,14 @@
       </c>
       <c r="C20" s="99">
         <f>C19/C10</f>
+        <v>-9.2228145917458232E-2</v>
+      </c>
+      <c r="D20" s="99">
+        <f>D19/D10</f>
         <v>-7.9730874225784606E-2</v>
       </c>
-      <c r="D20" s="99">
-        <f t="shared" ref="D20:F20" si="5">D19/D10</f>
-        <v>-8.5623709623040334E-2</v>
-      </c>
       <c r="E20" s="99">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="E20:F20" si="5">E19/E10</f>
         <v>-8.7978209802274554E-2</v>
       </c>
       <c r="F20" s="99">
@@ -4393,14 +4393,14 @@
       </c>
       <c r="C21" s="26">
         <f>C10*C16</f>
+        <v>331.03031190993079</v>
+      </c>
+      <c r="D21" s="26">
+        <f>D10*D16</f>
         <v>329.03418306602072</v>
       </c>
-      <c r="D21" s="26">
-        <f t="shared" ref="D21:F21" si="6">D10*D16</f>
-        <v>328.63931749161634</v>
-      </c>
       <c r="E21" s="26">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="E21:F21" si="6">E10*E16</f>
         <v>339.13663393167838</v>
       </c>
       <c r="F21" s="26">
@@ -4417,14 +4417,14 @@
       </c>
       <c r="C22" s="28">
         <f>C11*C16</f>
+        <v>276.54651992475516</v>
+      </c>
+      <c r="D22" s="28">
+        <f>D11*D16</f>
         <v>254.90803885100226</v>
       </c>
-      <c r="D22" s="28">
-        <f t="shared" ref="D22:F22" si="7">D11*D16</f>
-        <v>268.47187237615452</v>
-      </c>
       <c r="E22" s="28">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="E22:F22" si="7">E11*E16</f>
         <v>271.92982456140351</v>
       </c>
       <c r="F22" s="28">

--- a/datos/2025-11-06-ejemplo-std-tecnico.xlsx
+++ b/datos/2025-11-06-ejemplo-std-tecnico.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="819" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B5BBDD-EBB7-4467-9734-177531AE2285}"/>
+  <xr:revisionPtr revIDLastSave="942" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{159D9C06-232E-4CFA-8C34-9265FF9920E2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
   <sheets>
-    <sheet name="Estándar de fab" sheetId="21" r:id="rId1"/>
-    <sheet name="Desviaciones" sheetId="19" r:id="rId2"/>
+    <sheet name="Estándar técnico" sheetId="21" r:id="rId1"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
@@ -24,7 +24,6 @@
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
-    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
     <definedName name="__123Graph_AGRAFIND" hidden="1">#REF!</definedName>
@@ -38,7 +37,6 @@
     <definedName name="__Amount_for_Gross_Profit_Monthly_ASDA_All_Unit_2" hidden="1">[2]pcQueryData!#REF!</definedName>
     <definedName name="__Amount_for_Gross_Profit_Monthly_TESCO_All_1" hidden="1">#REF!</definedName>
     <definedName name="__Amount_for_Monthly_1" hidden="1">[3]pcQueryData!$A$4</definedName>
-    <definedName name="__c" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="__c" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="__c" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="_100_PV">#REF!</definedName>
@@ -166,162 +164,112 @@
     <definedName name="_pcSlicerSheet8_Slicer2" hidden="1">#REF!</definedName>
     <definedName name="_pcSlicerSheet9_Slicer1" hidden="1">#REF!</definedName>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
-    <definedName name="a" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="a" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="a" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="A_impresión_IM">#REF!</definedName>
     <definedName name="aaa" hidden="1">#REF!</definedName>
     <definedName name="aaaa" hidden="1">#REF!</definedName>
-    <definedName name="aaaaa" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aaaaa" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aaaaa" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="aaaaaaaaaaaaaaaa" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aaaaaaaaaaaaaaaa" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aaaaaaaaaaaaaaaa" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="AASAS" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="AASAS" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="AASAS" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ADV" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="ADV" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="ADV" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
-    <definedName name="ana" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="ana" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="ana" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="anscount" hidden="1">1</definedName>
-    <definedName name="ardqer" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ardqer" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ardqer" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ASD" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ASD" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ASD" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ASDF" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ASDF" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ASDF" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="asdfas" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="asdfas" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="asdfas" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="aùsw" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aùsw" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="aùsw" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="bbbbb" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="bbbbb" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="bbbbb" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="bd">#REF!</definedName>
-    <definedName name="bimes" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
     <definedName name="bimes" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
     <definedName name="bimes" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
     <definedName name="bof">"ComboBox1"</definedName>
-    <definedName name="byikbyuj" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byikbyuj" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byikbyuj" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="byubtyuj" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byubtyuj" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byubtyuj" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="byukkty" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byukkty" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byukkty" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="byuku" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byuku" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="byuku" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="č" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="č" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="č" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
-    <definedName name="cc" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cc" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cc" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ccc" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ccc" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ccc" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="cccc" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cccc" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cccc" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="CCSFDFRDF" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="CCSFDFRDF" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="CCSFDFRDF" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="cdf" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cdf" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="cdf" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="CDVF" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="CDVF" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="CDVF" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="copie" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="copie" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="copie" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
-    <definedName name="D" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="D" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="D" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="DAFreofè0eirfh" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DAFreofè0eirfh" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DAFreofè0eirfh" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="dd">#REF!</definedName>
-    <definedName name="DDD" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="DDD" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="DDD" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
-    <definedName name="DDDDD" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DDDDD" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DDDDD" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ddddddd" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ddddddd" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ddddddd" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ddjdjdj" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ddjdjdj" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ddjdjdj" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="dfa" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="dfa" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="dfa" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="DFda" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DFda" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DFda" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="DFRSFG" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DFRSFG" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DFRSFG" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="djdjdjd" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="djdjdjd" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="djdjdjd" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="dqdqdqd" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="dqdqdqd" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="dqdqdqd" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="DRAGAN" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="DRAGAN" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="DRAGAN" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
-    <definedName name="draganć" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="draganć" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="draganć" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
-    <definedName name="DSFSDGFG" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DSFSDGFG" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="DSFSDGFG" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="dthrrr" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="dthrrr" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="dthrrr" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ECA" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="ECA" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="ECA" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
-    <definedName name="ECARTBM" localSheetId="1" hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
     <definedName name="ECARTBM" localSheetId="0" hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
     <definedName name="ECARTBM" hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
-    <definedName name="eeeee" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="eeeee" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="eeeee" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="eerreerr" hidden="1">#REF!</definedName>
-    <definedName name="efazefze" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="efazefze" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="efazefze" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="ehethrer" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ehethrer" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ehethrer" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="ere" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ere" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ere" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ertetq" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertetq" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertetq" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="ertetqe" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertetqe" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertetqe" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="ertwert" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertwert" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertwert" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="ertwet" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertwet" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ertwet" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="EssLatest">"JAN"</definedName>
@@ -376,122 +324,84 @@
     <definedName name="ExactAddinConnection" hidden="1">"900"</definedName>
     <definedName name="ExactAddinConnection.900" hidden="1">"SRVSQLCZ;900;skubistova;1"</definedName>
     <definedName name="ExactAddinReports" hidden="1">1</definedName>
-    <definedName name="EXCEL" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="EXCEL" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="EXCEL" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
-    <definedName name="ezfzef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ezfzef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ezfzef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="fazefzef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fazefzef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fazefzef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="FDDSFDSGF" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="FDDSFDSGF" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="FDDSFDSGF" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="fdsdsgfsggd" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"DIVISION";#N/A,#N/A,FALSE,"ED CAT";#N/A,#N/A,FALSE,"ED CAREL";#N/A,#N/A,FALSE,"ED JORT";#N/A,#N/A,FALSE,"ED VEYS";#N/A,#N/A,FALSE,"ED ORBEC";#N/A,#N/A,FALSE,"ED CLECY"}</definedName>
     <definedName name="fdsdsgfsggd" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"DIVISION";#N/A,#N/A,FALSE,"ED CAT";#N/A,#N/A,FALSE,"ED CAREL";#N/A,#N/A,FALSE,"ED JORT";#N/A,#N/A,FALSE,"ED VEYS";#N/A,#N/A,FALSE,"ED ORBEC";#N/A,#N/A,FALSE,"ED CLECY"}</definedName>
     <definedName name="fdsdsgfsggd" hidden="1">{#N/A,#N/A,FALSE,"DIVISION";#N/A,#N/A,FALSE,"ED CAT";#N/A,#N/A,FALSE,"ED CAREL";#N/A,#N/A,FALSE,"ED JORT";#N/A,#N/A,FALSE,"ED VEYS";#N/A,#N/A,FALSE,"ED ORBEC";#N/A,#N/A,FALSE,"ED CLECY"}</definedName>
-    <definedName name="fdzfzefzef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fdzfzefzef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fdzfzefzef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="feazefzaef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="feazefzaef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="feazefzaef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="fere" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fere" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fere" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="ferw" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ferw" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ferw" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="ffff" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ffff" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ffff" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="ffffffffff" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ffffffffff" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ffffffffff" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="fg" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="fg" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="fg" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="fgffg" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="fgffg" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="fgffg" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="FSDG" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="FSDG" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="FSDG" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="fterearez" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fterearez" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fterearez" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="fzfzfef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fzfzfef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="fzfzfef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="GBP">'[6]Nrj présentat°'!$AR$2</definedName>
-    <definedName name="gegege" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gegege" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gegege" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="GF" hidden="1">[7]ACTIVITE!#REF!</definedName>
-    <definedName name="gfhkkmh" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="gfhkkmh" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="gfhkkmh" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="GG" hidden="1">[7]ACTIVITE!#REF!</definedName>
-    <definedName name="GGGG" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="GGGG" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="GGGG" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ggggg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ggggg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ggggg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="ggggggggggg" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ggggggggggg" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ggggggggggg" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="GHJ" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="GHJ" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="GHJ" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="gsdgsd" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gsdgsd" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gsdgsd" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="gtrgtrg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gtrgtrg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gtrgtrg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="gtrztrgr" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gtrztrgr" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gtrztrgr" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="gzgtzgz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgtzgz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgtzgz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="gzgzgz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgzgz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgzgz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="gzgzgzgt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgzgzgt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gzgzgzgt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="gztgrtrg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gztgrtrg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gztgrtrg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="gztgzgt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gztgzgt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="gztgzgt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="hbhajx" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hbhajx" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hbhajx" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="hfderfPOURE" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hfderfPOURE" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hfderfPOURE" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="hfhfth" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hfhfth" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hfhfth" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="hg" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hg" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hg" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="hhfxhxfh" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hhfxhxfh" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hhfxhxfh" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="hhhh" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hhhh" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hhhh" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="hhhhhhh" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hhhhhhh" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="hhhhhhh" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="HTML_CodePage" hidden="1">1250</definedName>
-    <definedName name="HTML_Control" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="HTML_Control" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="HTML_Control" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="HTML_Description" hidden="1">""</definedName>
@@ -506,437 +416,299 @@
     <definedName name="HTML_OS" hidden="1">0</definedName>
     <definedName name="HTML_PathFile" hidden="1">"C:\My Documents\MyHTML.htm"</definedName>
     <definedName name="HTML_Title" hidden="1">"Moja PRODAJA  II VELJAČA '2001"</definedName>
-    <definedName name="hzthzhr" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hzthzhr" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="hzthzhr" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="iiiiii" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="iiiiii" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="iiiiii" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="iiiiiiii" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="iiiiiiii" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="iiiiiiii" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="IRI_WorkspaceId" hidden="1">"bc7b7ef8a7ba454b9c6b30466fcd76e0"</definedName>
     <definedName name="ITAPLASPIC">#REF!</definedName>
-    <definedName name="IZVQ01" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="IZVQ01" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="IZVQ01" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
-    <definedName name="j" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="j" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="j" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="jcjfjfjjf" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jcjfjfjjf" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jcjfjfjjf" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="jdjdjdj" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="jdjdjdj" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="jdjdjdj" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="jej" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="jej" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="jej" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
-    <definedName name="jjfhfh" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjfhfh" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjfhfh" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="jjj" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjj" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjj" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="jjjjj" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjjjj" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="jjjjj" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="kfkfkfk" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kfkfkfk" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kfkfkfk" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="kfkfkfkfkkf" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kfkfkfkfkkf" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kfkfkfkfkkf" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="khkhkhk" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="khkhkhk" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="khkhkhk" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="khkk" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="khkk" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="khkk" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="kirirtir" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kirirtir" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kirirtir" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="kjfsoyiupo6rhtgz" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kjfsoyiupo6rhtgz" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kjfsoyiupo6rhtgz" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="kjhjhkjh" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="kjhjhkjh" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="kjhjhkjh" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
-    <definedName name="kk" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kk" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="kk" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="kkkkk" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kkkkk" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="kkkkk" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="LLL" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="LLL" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="LLL" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="m" localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="m" localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="m" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="MARTESANA">#REF!</definedName>
-    <definedName name="minnii" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="minnii" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="minnii" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="MOIS">[8]Grille!$B$3:$C$14</definedName>
     <definedName name="Month_No.">7</definedName>
-    <definedName name="nico" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="nico" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="nico" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="NUEVA" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="NUEVA" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="NUEVA" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="nueva1" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="nueva1" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="nueva1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ñ" hidden="1">#REF!</definedName>
-    <definedName name="ño" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ño" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ño" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ODRŽ." localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="ODRŽ." localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="ODRŽ." hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
-    <definedName name="òflfgfppfpf" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="òflfgfppfpf" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="òflfgfppfpf" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="OIOIIUIUG" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="OIOIIUIUG" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="OIOIIUIUG" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ooo" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ooo" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ooo" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="oooooo" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="oooooo" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="oooooo" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="P_HostName">#REF!</definedName>
     <definedName name="P_ServerName">#REF!</definedName>
-    <definedName name="pippo" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="pippo" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="pippo" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="pluto" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="pluto" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="pluto" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="PO" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="PO" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="PO" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="poùH" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="poùH" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="poùH" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ppp" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ppp" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ppp" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="PROD." localSheetId="1" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="PROD." localSheetId="0" hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
     <definedName name="PROD." hidden="1">{"'domaće količine'!$K$34:$P$47"}</definedName>
-    <definedName name="prw" localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="prw" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="prw" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
-    <definedName name="QQQQQQQQQQQQ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="QQQQQQQQQQQQ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="QQQQQQQQQQQQ" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="qw" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="qw" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="qw" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="reter" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="reter" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="reter" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="rgeegeqg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rgeegeqg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rgeegeqg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="rrrrrr" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rrrrrr" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rrrrrr" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="rteqtq" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rteqtq" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rteqtq" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="rtgtgrzg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtgtgrzg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtgtgrzg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="rtherrh" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtherrh" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtherrh" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="rtqtr" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtqtr" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtqtr" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="rtqtrq" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtqtrq" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="rtqtrq" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="sa" hidden="1">#REF!</definedName>
     <definedName name="SAPBEXrevision" hidden="1">3</definedName>
     <definedName name="SAPBEXsysID" hidden="1">"BPP"</definedName>
     <definedName name="SAPBEXwbID" hidden="1">"4GNIIN8XAB6OYSDJFHQ7XQLUA"</definedName>
-    <definedName name="sd" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sd" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sd" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="SDFDSJF" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SDFDSJF" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SDFDSJF" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="sdsd" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sdsd" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sdsd" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="SEDSDS" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SEDSDS" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SEDSDS" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sencount" hidden="1">1</definedName>
-    <definedName name="SSSADADSF" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SSSADADSF" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="SSSADADSF" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ssss" hidden="1">#REF!</definedName>
-    <definedName name="sssssss" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sssssss" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="sssssss" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ssssssssssssssssssssssssss" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ssssssssssssssssssssssssss" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ssssssssssssssssssssssssss" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="stsrhs" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="stsrhs" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="stsrhs" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="Sweden" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="Sweden" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="Sweden" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="t" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="T04CC" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="T04CC" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="T04CC" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="t79oto97t" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t79oto97t" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t79oto97t" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="t7u74u" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7u74u" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7u74u" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="t7u75" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7u75" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7u75" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="t7ur7u" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7ur7u" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="t7ur7u" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="tgfcvds" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tgfcvds" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tgfcvds" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="tgrgg" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tgrgg" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tgrgg" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="tgzgtgrrz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tgzgtgrrz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tgzgtgrrz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="thertherth" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="thertherth" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="thertherth" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="thzsrhrzhtz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="thzsrhrzhtz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="thzsrhrzhtz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="tikl679o679o" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tikl679o679o" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tikl679o679o" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="TM1REBUILDOPTION">0</definedName>
-    <definedName name="toma" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="toma" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="toma" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="trjk5i57" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="trjk5i57" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="trjk5i57" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="tt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="tttt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="tttttt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttttt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttttt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="tttttttttttt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttttttttttt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="tttttttttttt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="ttttttttttttt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ttttttttttttt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ttttttttttttt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="tyiltu9ol" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tyiltu9ol" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="tyiltu9ol" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ugkj" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ugkj" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ugkj" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ukkkk" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ukkkk" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="ukkkk" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="USD">'[6]Nrj présentat°'!$AR$3</definedName>
-    <definedName name="uttkjg" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="uttkjg" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="uttkjg" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="uuuu" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="uuuu" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="uuuu" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="uuuuuu" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="uuuuuu" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="uuuuuu" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="v6uyjyu" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="v6uyjyu" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="v6uyjyu" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="vcbbxb" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="vcbbxb" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="vcbbxb" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="vvvv" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvv" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvv" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="vvvvbbbb" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvbbbb" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvbbbb" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="vvvvvv" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvvv" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvvv" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="vvvvvvvv" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvvvvv" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="vvvvvvvv" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="w" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="w" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="w" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="we" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="we" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="we" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="wer" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="wer" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="wer" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
-    <definedName name="wetrwrt" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wetrwrt" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wetrwrt" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="wewe" localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wewe" localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wewe" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="wrn.CCC." localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.CCC." localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.CCC." hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="wrn.Charges." localSheetId="1" hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Charges." localSheetId="0" hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Charges." hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)"}</definedName>
-    <definedName name="wrn.Charges._.Clécy." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"Evol98";#N/A,#N/A,FALSE,"Saisie98"}</definedName>
     <definedName name="wrn.Charges._.Clécy." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"Evol98";#N/A,#N/A,FALSE,"Saisie98"}</definedName>
     <definedName name="wrn.Charges._.Clécy." hidden="1">{#N/A,#N/A,FALSE,"Evol98";#N/A,#N/A,FALSE,"Saisie98"}</definedName>
-    <definedName name="wrn.CLECY." localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="wrn.CLECY." localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="wrn.CLECY." hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"1A-TB 240";#N/A,#N/A,TRUE,"1B-TB 250";#N/A,#N/A,TRUE,"1D-Tr 240";#N/A,#N/A,TRUE,"1E-Tr 250";#N/A,#N/A,TRUE,"1M-Tr 250 60%";#N/A,#N/A,TRUE,"5A-Cru 240";#N/A,#N/A,TRUE,"5B-Cru 250";#N/A,#N/A,TRUE,"5D-Bio 250";#N/A,#N/A,TRUE,"3B-TB 320";#N/A,#N/A,TRUE,"3C-TB 350";#N/A,#N/A,TRUE,"Sérum";#N/A,#N/A,TRUE,"Recap Mat";#N/A,#N/A,TRUE,"ING CAM-TB";#N/A,#N/A,TRUE,"ING CAM-60%";#N/A,#N/A,TRUE,"ING CAM-Cru";#N/A,#N/A,TRUE,"ING COULO -52%";#N/A,#N/A,TRUE,"Recap Ing";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"Répart_charges";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"Synthèse";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
-    <definedName name="wrn.CNQGLOBAL." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RODEZ";#N/A,#N/A,FALSE,"BLEU CAUSSES";#N/A,#N/A,FALSE,"BLOC PAST";#N/A,#N/A,FALSE,"PENA";#N/A,#N/A,FALSE,"BUCHES";"RONDELEBASE",#N/A,FALSE,"RONDELE";"LONS",#N/A,FALSE,"RONDELE";#N/A,#N/A,FALSE,"UHT";#N/A,#N/A,FALSE,"POUDRE LAIT";#N/A,#N/A,FALSE,"POUDRE SER"}</definedName>
     <definedName name="wrn.CNQGLOBAL." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RODEZ";#N/A,#N/A,FALSE,"BLEU CAUSSES";#N/A,#N/A,FALSE,"BLOC PAST";#N/A,#N/A,FALSE,"PENA";#N/A,#N/A,FALSE,"BUCHES";"RONDELEBASE",#N/A,FALSE,"RONDELE";"LONS",#N/A,FALSE,"RONDELE";#N/A,#N/A,FALSE,"UHT";#N/A,#N/A,FALSE,"POUDRE LAIT";#N/A,#N/A,FALSE,"POUDRE SER"}</definedName>
     <definedName name="wrn.CNQGLOBAL." hidden="1">{#N/A,#N/A,FALSE,"RODEZ";#N/A,#N/A,FALSE,"BLEU CAUSSES";#N/A,#N/A,FALSE,"BLOC PAST";#N/A,#N/A,FALSE,"PENA";#N/A,#N/A,FALSE,"BUCHES";"RONDELEBASE",#N/A,FALSE,"RONDELE";"LONS",#N/A,FALSE,"RONDELE";#N/A,#N/A,FALSE,"UHT";#N/A,#N/A,FALSE,"POUDRE LAIT";#N/A,#N/A,FALSE,"POUDRE SER"}</definedName>
-    <definedName name="wrn.COMMENTAIRES." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"EC COMM-c";#N/A,#N/A,FALSE,"EC PAR PDTS-c";#N/A,#N/A,FALSE,"EC MAT-c";#N/A,#N/A,FALSE,"SUIVI HAUSSES-c"}</definedName>
     <definedName name="wrn.COMMENTAIRES." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"EC COMM-c";#N/A,#N/A,FALSE,"EC PAR PDTS-c";#N/A,#N/A,FALSE,"EC MAT-c";#N/A,#N/A,FALSE,"SUIVI HAUSSES-c"}</definedName>
     <definedName name="wrn.COMMENTAIRES." hidden="1">{#N/A,#N/A,FALSE,"EC COMM-c";#N/A,#N/A,FALSE,"EC PAR PDTS-c";#N/A,#N/A,FALSE,"EC MAT-c";#N/A,#N/A,FALSE,"SUIVI HAUSSES-c"}</definedName>
-    <definedName name="wrn.Complet." localSheetId="1" hidden="1">{"fr_collecte",#N/A,FALSE,"Fr_SA";"Fr_holding",#N/A,FALSE,"Fr_SA";"Frais_from",#N/A,FALSE,"Frs";"Couverture",#N/A,FALSE,"Frs";"Activité",#N/A,FALSE,"Act";"Act_commentaires",#N/A,FALSE,"Act";"Eff_personnel",#N/A,FALSE,"Eff";"Rendement",#N/A,FALSE,"Rdt";"Péreq",#N/A,FALSE,"Péreq";"récapit_mat",#N/A,FALSE,"récap_matière";#N/A,#N/A,FALSE,"Pci";"Ing_ingrédients",#N/A,FALSE,"Ing";"pci_évolution",#N/A,FALSE,"Pci";"pci_CA",#N/A,FALSE,"Pci";"pci_amélioration",#N/A,FALSE,"Pci";"SIG_Vercel",#N/A,FALSE,"Pci";"SIG_Philipona",#N/A,FALSE,"Pci"}</definedName>
     <definedName name="wrn.Complet." localSheetId="0" hidden="1">{"fr_collecte",#N/A,FALSE,"Fr_SA";"Fr_holding",#N/A,FALSE,"Fr_SA";"Frais_from",#N/A,FALSE,"Frs";"Couverture",#N/A,FALSE,"Frs";"Activité",#N/A,FALSE,"Act";"Act_commentaires",#N/A,FALSE,"Act";"Eff_personnel",#N/A,FALSE,"Eff";"Rendement",#N/A,FALSE,"Rdt";"Péreq",#N/A,FALSE,"Péreq";"récapit_mat",#N/A,FALSE,"récap_matière";#N/A,#N/A,FALSE,"Pci";"Ing_ingrédients",#N/A,FALSE,"Ing";"pci_évolution",#N/A,FALSE,"Pci";"pci_CA",#N/A,FALSE,"Pci";"pci_amélioration",#N/A,FALSE,"Pci";"SIG_Vercel",#N/A,FALSE,"Pci";"SIG_Philipona",#N/A,FALSE,"Pci"}</definedName>
     <definedName name="wrn.Complet." hidden="1">{"fr_collecte",#N/A,FALSE,"Fr_SA";"Fr_holding",#N/A,FALSE,"Fr_SA";"Frais_from",#N/A,FALSE,"Frs";"Couverture",#N/A,FALSE,"Frs";"Activité",#N/A,FALSE,"Act";"Act_commentaires",#N/A,FALSE,"Act";"Eff_personnel",#N/A,FALSE,"Eff";"Rendement",#N/A,FALSE,"Rdt";"Péreq",#N/A,FALSE,"Péreq";"récapit_mat",#N/A,FALSE,"récap_matière";#N/A,#N/A,FALSE,"Pci";"Ing_ingrédients",#N/A,FALSE,"Ing";"pci_évolution",#N/A,FALSE,"Pci";"pci_CA",#N/A,FALSE,"Pci";"pci_amélioration",#N/A,FALSE,"Pci";"SIG_Vercel",#N/A,FALSE,"Pci";"SIG_Philipona",#N/A,FALSE,"Pci"}</definedName>
-    <definedName name="wrn.CUMUL." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="wrn.CUMUL." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="wrn.CUMUL." hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
-    <definedName name="wrn.EDITION." localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="wrn.EDITION." localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
     <definedName name="wrn.EDITION." hidden="1">{#N/A,#N/A,TRUE,"VOLUMES";#N/A,#N/A,TRUE,"RDT CAM";#N/A,#N/A,TRUE,"RDT BDP";#N/A,#N/A,TRUE,"RDT LIV250";#N/A,#N/A,TRUE,"RDT LIV500";#N/A,#N/A,TRUE,"ING CAM";#N/A,#N/A,TRUE,"ING BDP";#N/A,#N/A,TRUE,"ING LIV";#N/A,#N/A,TRUE,"CHARGES";#N/A,#N/A,TRUE,"ENERGIES";#N/A,#N/A,TRUE,"PRODCHIM";#N/A,#N/A,TRUE,"EFFECTIF";#N/A,#N/A,TRUE,"PRIX CESSION";#N/A,#N/A,TRUE,"CPTE EXPLOIT";#N/A,#N/A,TRUE,"CONTROLE"}</definedName>
-    <definedName name="wrn.ex." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="wrn.ex." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
     <definedName name="wrn.ex." hidden="1">{#N/A,#N/A,FALSE,"ANALYSE";#N/A,#N/A,FALSE,"PM VALEUR"}</definedName>
-    <definedName name="wrn.Impression._.totale." localSheetId="1" hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)";"Ratios activités",#N/A,FALSE,"Feuil1 (2)";"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Impression._.totale." localSheetId="0" hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)";"Ratios activités",#N/A,FALSE,"Feuil1 (2)";"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Impression._.totale." hidden="1">{"Analyse charges",#N/A,FALSE,"Feuil1 (2)";"Ratios activités",#N/A,FALSE,"Feuil1 (2)";"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
-    <definedName name="wrn.Indicateurs." localSheetId="1" hidden="1">{"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Indicateurs." localSheetId="0" hidden="1">{"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Indicateurs." hidden="1">{"Indicateurs",#N/A,FALSE,"Feuil1 (2)"}</definedName>
-    <definedName name="wrn.MENSUEL." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
     <definedName name="wrn.MENSUEL." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
     <definedName name="wrn.MENSUEL." hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge";#N/A,#N/A,FALSE,"cumul I";#N/A,#N/A,FALSE,"cumul II";#N/A,#N/A,FALSE,"cumul III"}</definedName>
-    <definedName name="wrn.MOYENNE." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="wrn.MOYENNE." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
     <definedName name="wrn.MOYENNE." hidden="1">{#N/A,#N/A,FALSE,"recap";#N/A,#N/A,FALSE,"matNeuf";#N/A,#N/A,FALSE,"matNdie";#N/A,#N/A,FALSE,"incNeuf";#N/A,#N/A,FALSE,"incNdie";#N/A,#N/A,FALSE,"volume";#N/A,#N/A,FALSE,"emballage";#N/A,#N/A,FALSE,"charge"}</definedName>
-    <definedName name="wrn.novgl." localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="wrn.novgl." localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="wrn.novgl." hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="wrn.Ratios." localSheetId="1" hidden="1">{"Ratios activités",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Ratios." localSheetId="0" hidden="1">{"Ratios activités",#N/A,FALSE,"Feuil1 (2)"}</definedName>
     <definedName name="wrn.Ratios." hidden="1">{"Ratios activités",#N/A,FALSE,"Feuil1 (2)"}</definedName>
-    <definedName name="wrn.REELBUD." localSheetId="1" hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
     <definedName name="wrn.REELBUD." localSheetId="0" hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
     <definedName name="wrn.REELBUD." hidden="1">{"DETAIL",#N/A,FALSE,"REELBUDGET";"TOTAL",#N/A,FALSE,"REELBUDGET"}</definedName>
-    <definedName name="wrn.Résultat." localSheetId="1" hidden="1">{"Struct",#N/A,FALSE,"Récap Struct";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Détail",#N/A,FALSE,"Chges Détail"}</definedName>
     <definedName name="wrn.Résultat." localSheetId="0" hidden="1">{"Struct",#N/A,FALSE,"Récap Struct";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Détail",#N/A,FALSE,"Chges Détail"}</definedName>
     <definedName name="wrn.Résultat." hidden="1">{"Struct",#N/A,FALSE,"Récap Struct";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Struct",#N/A,FALSE,"Récap Struct";"Chges Total",#N/A,FALSE,"Chges Récap";"Chges Détail",#N/A,FALSE,"Chges Récap";"Détail",#N/A,FALSE,"Chges Détail"}</definedName>
-    <definedName name="wrn.SPA1." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.SPA1." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.SPA1." hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="wrn.SPM1." localSheetId="1" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.SPM1." localSheetId="0" hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn.SPM1." hidden="1">{"SPM1",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="wrn.SYNTHESE." localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="wrn.SYNTHESE." localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
     <definedName name="wrn.SYNTHESE." hidden="1">{#N/A,#N/A,TRUE,"ANALYSE";#N/A,#N/A,TRUE,"PM VOLUME";#N/A,#N/A,TRUE,"PM VALEUR";#N/A,#N/A,TRUE,"AR1";#N/A,#N/A,TRUE,"AR2";#N/A,#N/A,TRUE,"RAF";#N/A,#N/A,TRUE,"BILAN";#N/A,#N/A,TRUE,"CASH FLOW";#N/A,#N/A,TRUE,"ETAT FI"}</definedName>
-    <definedName name="wrn.TABLEAUX." localSheetId="1" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="wrn.TABLEAUX." localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
     <definedName name="wrn.TABLEAUX." hidden="1">{#N/A,#N/A,TRUE,"EC COMM-t";#N/A,#N/A,TRUE,"EC PAR PDTS-t";#N/A,#N/A,TRUE,"EC MAT-t";#N/A,#N/A,TRUE,"SUIVI HAUSSES-t"}</definedName>
-    <definedName name="wrn1.CCC." localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn1.CCC." localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wrn1.CCC." hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="wwww" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wwww" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wwww" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="wwwwww" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="wwwwww" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="wwwwww" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="wwwwwwwwwwww" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wwwwwwwwwwww" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="wwwwwwwwwwww" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="ybukkbyitkituk" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ybukkbyitkituk" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="ybukkbyitkituk" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="yertyyyy" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yertyyyy" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yertyyyy" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="yeyyyy" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yeyyyy" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yeyyyy" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="yrnukuilky8u" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="yrnukuilky8u" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="yrnukuilky8u" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="YY" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="YY" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="YY" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="yyqeyqy" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyqeyqy" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyqeyqy" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="yyyyy" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyyyy" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyyyy" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="yyyyyy" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyyyyy" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="yyyyyy" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="zefzaefze" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zefzaefze" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zefzaefze" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="zefzerfzef" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zefzerfzef" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zefzerfzef" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="zegtrgzgt" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zegtrgzgt" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zegtrgzgt" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zz" hidden="1">#REF!</definedName>
-    <definedName name="zzfzafz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzfzafz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzfzafz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzz" hidden="1">#REF!</definedName>
     <definedName name="zzzzz" hidden="1">#REF!</definedName>
-    <definedName name="zzzzzz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzzzzz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzzzzz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="zzzzzzz" localSheetId="1" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzzzzzz" localSheetId="0" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
     <definedName name="zzzzzzz" hidden="1">{"glinput",#N/A,FALSE,"NOVGL";"page2",#N/A,FALSE,"NOVGL";"veveypl",#N/A,FALSE,"NOVGL";"compl",#N/A,FALSE,"NOVGL";"asset",#N/A,FALSE,"NOVGL";"liab",#N/A,FALSE,"NOVGL";"assetgl",#N/A,FALSE,"NOVGL";"liabgl",#N/A,FALSE,"NOVGL";"balast",#N/A,FALSE,"NOVGL";"ballib",#N/A,FALSE,"NOVGL"}</definedName>
-    <definedName name="zzzzzzzzzz" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzz" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzz" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="zzzzzzzzzzzzz" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzz" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzz" hidden="1">{#N/A,#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="zzzzzzzzzzzzzz" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzzz" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzzz" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
-    <definedName name="zzzzzzzzzzzzzzzzzz" localSheetId="1" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzzzzzzz" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzzzzzzz" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
   </definedNames>
@@ -959,24 +731,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>ESM</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>MP</t>
   </si>
   <si>
     <t>Litraje unitario</t>
   </si>
   <si>
     <t>MG teórica en la cuba (g/L)</t>
-  </si>
-  <si>
-    <t>EST</t>
   </si>
   <si>
     <t>Mezcla</t>
@@ -991,15 +754,6 @@
     <t>Bajo en MG</t>
   </si>
   <si>
-    <t>Análisis de desviaciones</t>
-  </si>
-  <si>
-    <t>Estándar</t>
-  </si>
-  <si>
-    <t>Real</t>
-  </si>
-  <si>
     <t>Fabricación, KG</t>
   </si>
   <si>
@@ -1009,142 +763,16 @@
     <t>G/ES</t>
   </si>
   <si>
-    <t>Litros leche puestos en fab (cuba)</t>
-  </si>
-  <si>
-    <t>Composición leche en cuba MG (g/L)</t>
-  </si>
-  <si>
-    <t>Composición leche en cuba MP (g/L)</t>
-  </si>
-  <si>
-    <t>KMG puestos en fabricacion (cuba)</t>
-  </si>
-  <si>
-    <t>KMP puestos en fabricacion (cuba)</t>
-  </si>
-  <si>
-    <t>factor MG/MP leche cubas</t>
-  </si>
-  <si>
     <t>Recup MG</t>
-  </si>
-  <si>
-    <t>Recup MP</t>
-  </si>
-  <si>
-    <t>Std</t>
-  </si>
-  <si>
-    <t>Dif</t>
-  </si>
-  <si>
-    <t>Valor</t>
   </si>
   <si>
     <t>Consumo MP/kg queso</t>
   </si>
   <si>
-    <t>MG leche compra</t>
-  </si>
-  <si>
-    <t>MP leche compra</t>
-  </si>
-  <si>
-    <t>Bdgt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desv </t>
-  </si>
-  <si>
-    <t>desv kg MP</t>
-  </si>
-  <si>
-    <t>desv kg MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MP € </t>
-  </si>
-  <si>
-    <t>MG €</t>
-  </si>
-  <si>
-    <t>TOTAL €</t>
-  </si>
-  <si>
-    <t>Desviaciones por composición queso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MG </t>
-  </si>
-  <si>
-    <t>Efecto EST (composición MG)</t>
-  </si>
-  <si>
-    <t>Efecto rendimiento (recup MG)</t>
-  </si>
-  <si>
-    <t>Efecto EST (composición ESM)</t>
-  </si>
-  <si>
-    <t>Efecto  rendimiento (recup MP)</t>
-  </si>
-  <si>
-    <t>Total explicado</t>
-  </si>
-  <si>
-    <t>Total efectos</t>
-  </si>
-  <si>
-    <t>EST (MG + ESM)</t>
-  </si>
-  <si>
-    <t>Recuperación (MG+MP)</t>
-  </si>
-  <si>
-    <t>Otros efectos no explicados</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>En azul:</t>
-  </si>
-  <si>
-    <t>Datos del estándar a completar</t>
-  </si>
-  <si>
-    <t>Datos reales de la fabricacion a comparar</t>
-  </si>
-  <si>
-    <t>En verde:</t>
-  </si>
-  <si>
-    <t>Sin color:</t>
-  </si>
-  <si>
-    <t>Celdas, calculadas, no modificar</t>
-  </si>
-  <si>
     <t>MG pérdida bruta en suero %</t>
   </si>
   <si>
-    <t>Otros efectos</t>
-  </si>
-  <si>
-    <t>€ desv</t>
-  </si>
-  <si>
     <t>Consumo MG/kg queso</t>
-  </si>
-  <si>
-    <t>Coste leche en cuba MG (coste compra MG)</t>
-  </si>
-  <si>
-    <t>Litraje unitario teórico (L/Kg)</t>
-  </si>
-  <si>
-    <t>MG pérdida bruta en suero (kg)</t>
   </si>
   <si>
     <t>Estándar de producto</t>
@@ -1218,22 +846,16 @@
   <si>
     <t>4. Cálculos</t>
   </si>
-  <si>
-    <t>Coste leche en cuba MP (coste compra MP)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="165" formatCode="#,##0.000_ ;[Red]\-#,##0.000\ "/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    <numFmt numFmtId="170" formatCode="#,##0.0_ ;[Red]\-#,##0.0\ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1275,7 +897,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1302,25 +924,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1331,7 +935,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1358,31 +962,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1404,101 +986,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1514,179 +1001,83 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="9" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="9" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares 2" xfId="2" xr:uid="{0DF497A4-B1A4-4A8E-B2C1-3A725AAFDCC2}"/>
@@ -4001,1207 +3392,435 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="79" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="79" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="79" t="s">
+      <c r="A1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>6</v>
-      </c>
-      <c r="E1" s="79" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="79" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82">
+      <c r="A2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18">
         <v>1</v>
       </c>
-      <c r="D2" s="82">
+      <c r="D2" s="18">
         <v>1</v>
       </c>
-      <c r="E2" s="82">
+      <c r="E2" s="18">
         <v>1</v>
       </c>
-      <c r="F2" s="82">
+      <c r="F2" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="86" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
+      <c r="A3" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="84" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3">
+      <c r="A4" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2">
         <v>0.55630000000000002</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>0.54949999999999999</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>0.5635</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>0.50470000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="85" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4">
+      <c r="A5" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3">
         <v>0.30049999999999999</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>0.30280000000000001</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>0.30930000000000002</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>0.20219999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="100" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="14">
+      <c r="B6" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="6">
         <f>C4-C5</f>
         <v>0.25580000000000003</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="6">
         <f>D4-D5</f>
         <v>0.24669999999999997</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="6">
         <f t="shared" ref="E6:F6" si="0">E4-E5</f>
         <v>0.25419999999999998</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="6">
         <f t="shared" si="0"/>
         <v>0.30250000000000005</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="101" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="16">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="7">
         <f>(1-C4)/(1-C5)</f>
         <v>0.63431022158684769</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="7">
         <f>(1-D4)/(1-D5)</f>
         <v>0.64615605278255883</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="7">
         <f t="shared" ref="E7:F7" si="1">(1-E4)/(1-E5)</f>
         <v>0.63196756913276386</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="7">
         <f t="shared" si="1"/>
         <v>0.62083228879418395</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="102" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="18">
+      <c r="A8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="8">
         <f>C5/C4</f>
         <v>0.54017616394031998</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="8">
         <f>D5/D4</f>
         <v>0.55104640582347597</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="8">
         <f t="shared" ref="E8:F8" si="2">E5/E4</f>
         <v>0.54889086069210291</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="8">
         <f t="shared" si="2"/>
         <v>0.40063404002377645</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="88" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="89"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
+      <c r="A9" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="90" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91">
+      <c r="A10" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27">
         <v>40.1</v>
       </c>
-      <c r="D10" s="91">
+      <c r="D10" s="27">
         <v>41.37</v>
       </c>
-      <c r="E10" s="91">
+      <c r="E10" s="27">
         <v>71.05</v>
       </c>
-      <c r="F10" s="91">
+      <c r="F10" s="27">
         <v>24.82</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="92" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93">
+      <c r="A11" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29">
         <v>33.5</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="29">
         <v>32.049999999999997</v>
       </c>
-      <c r="E11" s="93">
+      <c r="E11" s="29">
         <v>56.97</v>
       </c>
-      <c r="F11" s="93">
+      <c r="F11" s="29">
         <v>33.659999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="94" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
+      <c r="A12" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="96" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="97"/>
-      <c r="C13" s="97">
+      <c r="A13" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33">
         <v>0.92498000000000002</v>
       </c>
-      <c r="D13" s="97">
+      <c r="D13" s="33">
         <v>0.96779999999999999</v>
       </c>
-      <c r="E13" s="97">
+      <c r="E13" s="33">
         <v>0.93479999999999996</v>
       </c>
-      <c r="F13" s="97">
+      <c r="F13" s="33">
         <v>0.97330000000000005</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
+      <c r="A14" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="103" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="21">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="9">
         <f>C13*C11</f>
         <v>30.986830000000001</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="9">
         <f>D13*D11</f>
         <v>31.017989999999998</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="9">
         <f>E13*E11</f>
         <v>53.255555999999999</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="9">
         <f>F13*F11</f>
         <v>32.761277999999997</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="104" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="80">
+      <c r="A16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="16">
         <f>C6*1000/C15</f>
         <v>8.2551199977538854</v>
       </c>
-      <c r="D16" s="80">
+      <c r="D16" s="16">
         <f>D6*1000/D15</f>
         <v>7.9534489501092756</v>
       </c>
-      <c r="E16" s="80">
+      <c r="E16" s="16">
         <f>E6*1000/E15</f>
         <v>4.7732108927752064</v>
       </c>
-      <c r="F16" s="80">
+      <c r="F16" s="16">
         <f>F6*1000/F15</f>
         <v>9.2334615273555585</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="103" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="21">
+      <c r="A17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="9">
         <f>C5*1000/C16</f>
         <v>36.401651348709926</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="9">
         <f>D5*1000/D16</f>
         <v>38.071533733279288</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="9">
         <f>E5*1000/E16</f>
         <v>64.79914819354839</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="9">
         <f>F5*1000/F16</f>
         <v>21.898612930909085</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="105" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="78">
+      <c r="A18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="14">
         <f>C17/C10</f>
         <v>0.9077718540825418</v>
       </c>
-      <c r="D18" s="78">
+      <c r="D18" s="14">
         <f>D17/D10</f>
         <v>0.92026912577421538</v>
       </c>
-      <c r="E18" s="78">
+      <c r="E18" s="14">
         <f t="shared" ref="E18:F18" si="3">E17/E10</f>
         <v>0.91202179019772545</v>
       </c>
-      <c r="F18" s="78">
+      <c r="F18" s="14">
         <f t="shared" si="3"/>
         <v>0.88229705603985031</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="72" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="74">
+      <c r="A19" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="13">
         <f>C17-C10</f>
         <v>-3.6983486512900754</v>
       </c>
-      <c r="D19" s="74">
+      <c r="D19" s="13">
         <f>D17-D10</f>
         <v>-3.298466266720709</v>
       </c>
-      <c r="E19" s="74">
+      <c r="E19" s="13">
         <f t="shared" ref="E19:F19" si="4">E17-E10</f>
         <v>-6.2508518064516068</v>
       </c>
-      <c r="F19" s="74">
+      <c r="F19" s="13">
         <f t="shared" si="4"/>
         <v>-2.9213870690909154</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="107" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="99">
+      <c r="A20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="35">
         <f>C19/C10</f>
         <v>-9.2228145917458232E-2</v>
       </c>
-      <c r="D20" s="99">
+      <c r="D20" s="35">
         <f>D19/D10</f>
         <v>-7.9730874225784606E-2</v>
       </c>
-      <c r="E20" s="99">
+      <c r="E20" s="35">
         <f t="shared" ref="E20:F20" si="5">E19/E10</f>
         <v>-8.7978209802274554E-2</v>
       </c>
-      <c r="F20" s="99">
+      <c r="F20" s="35">
         <f t="shared" si="5"/>
         <v>-0.11770294396014969</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="72" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="108" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="26">
+      <c r="A21" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="10">
         <f>C10*C16</f>
         <v>331.03031190993079</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="10">
         <f>D10*D16</f>
         <v>329.03418306602072</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="10">
         <f t="shared" ref="E21:F21" si="6">E10*E16</f>
         <v>339.13663393167838</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="10">
         <f t="shared" si="6"/>
         <v>229.17451510896495</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="109" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="28">
+      <c r="A22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="11">
         <f>C11*C16</f>
         <v>276.54651992475516</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="11">
         <f>D11*D16</f>
         <v>254.90803885100226</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="11">
         <f t="shared" ref="E22:F22" si="7">E11*E16</f>
         <v>271.92982456140351</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="11">
         <f t="shared" si="7"/>
         <v>310.79831501078809</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="77" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54D5B130-24F3-48FC-83F1-D6CDA4B85E81}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="9" width="10.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="64">
-        <v>11.2</v>
-      </c>
-      <c r="E2" s="67" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="10">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C3" s="62">
-        <v>0.57550000000000001</v>
-      </c>
-      <c r="E3" s="61" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="11">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="C4" s="63">
-        <v>0.31709999999999999</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="14">
-        <f>B3-B4</f>
-        <v>0.27</v>
-      </c>
-      <c r="C5" s="14">
-        <f>C3-C4</f>
-        <v>0.25840000000000002</v>
-      </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="13"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="16">
-        <f>(1-B3)/(1-B4)</f>
-        <v>0.625</v>
-      </c>
-      <c r="C6" s="16">
-        <f>(1-C3)/(1-C4)</f>
-        <v>0.62161370625274559</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="18">
-        <f>B4/B3</f>
-        <v>0.50909090909090915</v>
-      </c>
-      <c r="C7" s="18">
-        <f>C4/C3</f>
-        <v>0.55099913119026933</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="65">
-        <v>105</v>
-      </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="21">
-        <f>B11*1000/C8</f>
-        <v>33.671552048102221</v>
-      </c>
-      <c r="C9" s="66">
-        <v>34.54</v>
-      </c>
-      <c r="E9" s="68"/>
-      <c r="I9" s="20"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="21">
-        <f>B12*1000/C8</f>
-        <v>29.298067141403866</v>
-      </c>
-      <c r="C10" s="66">
-        <v>32.200000000000003</v>
-      </c>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="I10" s="20"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="21">
-        <f>B$4/B$15*C$2</f>
-        <v>3.5355129650507329</v>
-      </c>
-      <c r="C11" s="21">
-        <f>C9*C8/1000</f>
-        <v>3.6267</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="68"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="21">
-        <f>C$2*B$5/B$16</f>
-        <v>3.076297049847406</v>
-      </c>
-      <c r="C12" s="21">
-        <f>C10*C8/1000</f>
-        <v>3.3810000000000007</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="68"/>
-      <c r="K12" s="12"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="23">
-        <f>B11/B12</f>
-        <v>1.1492755438640443</v>
-      </c>
-      <c r="C13" s="23">
-        <f>C11/C12</f>
-        <v>1.0726708074534159</v>
-      </c>
-      <c r="E13" s="68"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="24">
-        <f>(B5*1000/B10)</f>
-        <v>9.2156249999999993</v>
-      </c>
-      <c r="C14" s="24">
-        <f>(C5*1000/C10)</f>
-        <v>8.024844720496894</v>
-      </c>
-      <c r="I14" s="12"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="11">
-        <v>0.88700000000000001</v>
-      </c>
-      <c r="C15" s="14">
-        <v>0.93200000000000005</v>
-      </c>
-      <c r="I15" s="12"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="11">
-        <v>0.98299999999999998</v>
-      </c>
-      <c r="C16" s="14">
-        <v>0.96499999999999997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="74">
-        <f>(B4*C2)-B11</f>
-        <v>-0.39951296505073275</v>
-      </c>
-      <c r="C17" s="74">
-        <f>(C4*C2)-C11</f>
-        <v>-7.5180000000000469E-2</v>
-      </c>
-      <c r="F17" s="22"/>
-      <c r="I17" s="12"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="73">
-        <f>B17/B11</f>
-        <v>-0.11299999999999998</v>
-      </c>
-      <c r="C18" s="25">
-        <f>C17/C11</f>
-        <v>-2.0729588882455255E-2</v>
-      </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="70"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="70"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="70"/>
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="26">
-        <f>B11/C2*1000</f>
-        <v>315.67080045095832</v>
-      </c>
-      <c r="C22" s="26">
-        <f>C9*C8/C2</f>
-        <v>323.8125</v>
-      </c>
-      <c r="D22" s="74">
-        <f>((B22-C22)*B24*C2/1000)</f>
-        <v>-0.45867078579481174</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="28">
-        <f>B12/C2*1000</f>
-        <v>274.66937945066127</v>
-      </c>
-      <c r="C23" s="29">
-        <f>C10*C8/C2</f>
-        <v>301.87500000000006</v>
-      </c>
-      <c r="D23" s="75">
-        <f>((B23-C23)*B25*C2/1000)</f>
-        <v>-2.714903285859616</v>
-      </c>
-      <c r="E23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="68">
-        <f>B11</f>
-        <v>3.5355129650507329</v>
-      </c>
-      <c r="G23" s="68">
-        <f>C11</f>
-        <v>3.6267</v>
-      </c>
-      <c r="H23" s="68">
-        <f>F23-G23</f>
-        <v>-9.1187034949267165E-2</v>
-      </c>
-      <c r="I23" s="68">
-        <f>H23*B24</f>
-        <v>-0.45867078579481385</v>
-      </c>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="32">
-        <v>5.03</v>
-      </c>
-      <c r="C24" s="32">
-        <v>5.03</v>
-      </c>
-      <c r="D24" s="74">
-        <f>(B24-C24)*C22*C2/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="68">
-        <f>B12</f>
-        <v>3.076297049847406</v>
-      </c>
-      <c r="G24" s="68">
-        <f>C12</f>
-        <v>3.3810000000000007</v>
-      </c>
-      <c r="H24" s="68">
-        <f>F24-G24</f>
-        <v>-0.30470295015259463</v>
-      </c>
-      <c r="I24" s="68">
-        <f>H24*B25</f>
-        <v>-2.7149032858596183</v>
-      </c>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="30">
-        <v>8.91</v>
-      </c>
-      <c r="C25" s="30">
-        <v>8.91</v>
-      </c>
-      <c r="D25" s="75">
-        <f>(B25-C25)*C23*C2/1000</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="68">
-        <f>SUM(I23:I24)</f>
-        <v>-3.1735740716544321</v>
-      </c>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="31"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="76">
-        <f>SUM(D22:D25)</f>
-        <v>-3.1735740716544276</v>
-      </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="39"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="42">
-        <f>B$4/B$15*C$2</f>
-        <v>3.5355129650507329</v>
-      </c>
-      <c r="C30" s="42">
-        <f>(C$4/C$15)*C$2</f>
-        <v>3.8106437768240342</v>
-      </c>
-      <c r="D30" s="43">
-        <f>B30-C30</f>
-        <v>-0.27513081177330134</v>
-      </c>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="43"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="46">
-        <f>B$4/B$15*C$2</f>
-        <v>3.5355129650507329</v>
-      </c>
-      <c r="C31" s="46">
-        <f>(C$4/B$15)*C$2</f>
-        <v>4.0039684329199545</v>
-      </c>
-      <c r="D31" s="47">
-        <f>B31-C31</f>
-        <v>-0.46845546786922165</v>
-      </c>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48">
-        <f>D31</f>
-        <v>-0.46845546786922165</v>
-      </c>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46">
-        <f t="shared" ref="H31:H33" si="0">F31*B$24</f>
-        <v>-2.3563310033821852</v>
-      </c>
-      <c r="I31" s="47">
-        <f t="shared" ref="I31:I33" si="1">SUM(G31:H31)</f>
-        <v>-2.3563310033821852</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="46">
-        <f>B$4/B$15*C$2</f>
-        <v>3.5355129650507329</v>
-      </c>
-      <c r="C32" s="46">
-        <f>(B$4/C$15)*C$2</f>
-        <v>3.3648068669527897</v>
-      </c>
-      <c r="D32" s="47">
-        <f>B32-C32</f>
-        <v>0.17070609809794313</v>
-      </c>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48">
-        <f>D32</f>
-        <v>0.17070609809794313</v>
-      </c>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46">
-        <f t="shared" si="0"/>
-        <v>0.85865167343265392</v>
-      </c>
-      <c r="I32" s="47">
-        <f t="shared" si="1"/>
-        <v>0.85865167343265392</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="50"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="52">
-        <f>(B15-C15)*(B4-C4)*C2</f>
-        <v>1.8698399999999997E-2</v>
-      </c>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53">
-        <f>D33</f>
-        <v>1.8698399999999997E-2</v>
-      </c>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50">
-        <f t="shared" si="0"/>
-        <v>9.4052951999999995E-2</v>
-      </c>
-      <c r="I33" s="52">
-        <f t="shared" si="1"/>
-        <v>9.4052951999999995E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" s="42">
-        <f>C$2*B$5/B$16</f>
-        <v>3.076297049847406</v>
-      </c>
-      <c r="C34" s="42">
-        <f>C2*C5/C16</f>
-        <v>2.9990466321243527</v>
-      </c>
-      <c r="D34" s="43">
-        <f>B34-C34</f>
-        <v>7.72504177230533E-2</v>
-      </c>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="43"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="46">
-        <f>C$2*B$5/B$16</f>
-        <v>3.076297049847406</v>
-      </c>
-      <c r="C35" s="46">
-        <f>C2*C5/B16</f>
-        <v>2.9441302136317398</v>
-      </c>
-      <c r="D35" s="47">
-        <f>B35-C35</f>
-        <v>0.13216683621566627</v>
-      </c>
-      <c r="E35" s="48">
-        <f>D35</f>
-        <v>0.13216683621566627</v>
-      </c>
-      <c r="F35" s="48"/>
-      <c r="G35" s="46">
-        <f>E35*B$25</f>
-        <v>1.1776065106815865</v>
-      </c>
-      <c r="H35" s="46"/>
-      <c r="I35" s="47">
-        <f>SUM(G35:H35)</f>
-        <v>1.1776065106815865</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="46">
-        <f>C$2*B$5/B$16</f>
-        <v>3.076297049847406</v>
-      </c>
-      <c r="C36" s="46">
-        <f>C2*B5/C16</f>
-        <v>3.1336787564766841</v>
-      </c>
-      <c r="D36" s="47">
-        <f>B36-C36</f>
-        <v>-5.7381706629278106E-2</v>
-      </c>
-      <c r="E36" s="48">
-        <f>D36</f>
-        <v>-5.7381706629278106E-2</v>
-      </c>
-      <c r="F36" s="48"/>
-      <c r="G36" s="46">
-        <f t="shared" ref="G36:G37" si="2">E36*B$25</f>
-        <v>-0.51127100606686793</v>
-      </c>
-      <c r="H36" s="46"/>
-      <c r="I36" s="47">
-        <f t="shared" ref="I36:I37" si="3">SUM(G36:H36)</f>
-        <v>-0.51127100606686793</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="75"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="50">
-        <f>(B16-C16)*(B5-C5)*C2</f>
-        <v>2.3385600000000017E-3</v>
-      </c>
-      <c r="E37" s="53">
-        <f>D37</f>
-        <v>2.3385600000000017E-3</v>
-      </c>
-      <c r="F37" s="53"/>
-      <c r="G37" s="50">
-        <f t="shared" si="2"/>
-        <v>2.0836569600000014E-2</v>
-      </c>
-      <c r="H37" s="50"/>
-      <c r="I37" s="52">
-        <f t="shared" si="3"/>
-        <v>2.0836569600000014E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="42"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="44">
-        <f>SUM(E30:E37)</f>
-        <v>7.7123689586388169E-2</v>
-      </c>
-      <c r="F38" s="44">
-        <f>SUM(F30:F37)</f>
-        <v>-0.27905096977127852</v>
-      </c>
-      <c r="G38" s="42">
-        <f>SUM(G30:G37)</f>
-        <v>0.6871720742147186</v>
-      </c>
-      <c r="H38" s="42">
-        <f>SUM(H30:H37)</f>
-        <v>-1.4036263779495313</v>
-      </c>
-      <c r="I38" s="43">
-        <f>SUM(I30:I37)</f>
-        <v>-0.71645430373481267</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="57"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="58" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="59">
-        <f>SUM(I31,I35)</f>
-        <v>-1.1787244927005986</v>
-      </c>
-      <c r="D41" s="12"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="46">
-        <f>SUM(I32,I36)</f>
-        <v>0.34738066736578599</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="58" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43" s="46">
-        <f>SUM(I33+I37)</f>
-        <v>0.11488952160000002</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="50">
-        <f>SUM(B41:B43)</f>
-        <v>-0.71645430373481267</v>
       </c>
     </row>
   </sheetData>

--- a/datos/2025-11-06-ejemplo-std-tecnico.xlsx
+++ b/datos/2025-11-06-ejemplo-std-tecnico.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="942" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{159D9C06-232E-4CFA-8C34-9265FF9920E2}"/>
+  <xr:revisionPtr revIDLastSave="947" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2D2943E-0DF3-410E-AD41-3C5911498EB0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
+    <workbookView xWindow="13215" yWindow="855" windowWidth="15390" windowHeight="14250" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
   <sheets>
     <sheet name="Estándar técnico" sheetId="21" r:id="rId1"/>
@@ -854,8 +854,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="165" formatCode="#,##0.000_ ;[Red]\-#,##0.000\ "/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -999,7 +999,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1017,13 +1017,13 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1053,15 +1053,15 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -1071,10 +1071,10 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2">
-        <v>0.55630000000000002</v>
+        <v>0.54849999999999999</v>
       </c>
       <c r="D4" s="2">
         <v>0.54949999999999999</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3">
-        <v>0.30049999999999999</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="D5" s="3">
         <v>0.30280000000000001</v>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C6" s="6">
         <f>C4-C5</f>
-        <v>0.25580000000000003</v>
+        <v>0.2505</v>
       </c>
       <c r="D6" s="6">
         <f>D4-D5</f>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C7" s="7">
         <f>(1-C4)/(1-C5)</f>
-        <v>0.63431022158684769</v>
+        <v>0.64316239316239321</v>
       </c>
       <c r="D7" s="7">
         <f>(1-D4)/(1-D5)</f>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="C8" s="8">
         <f>C5/C4</f>
-        <v>0.54017616394031998</v>
+        <v>0.54329990884229717</v>
       </c>
       <c r="D8" s="8">
         <f>D5/D4</f>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B10" s="27"/>
       <c r="C10" s="27">
-        <v>40.1</v>
+        <v>38.1</v>
       </c>
       <c r="D10" s="27">
         <v>41.37</v>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="29">
-        <v>33.5</v>
+        <v>32.1</v>
       </c>
       <c r="D11" s="29">
         <v>32.049999999999997</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B13" s="33"/>
       <c r="C13" s="33">
-        <v>0.92498000000000002</v>
+        <v>0.9446</v>
       </c>
       <c r="D13" s="33">
         <v>0.96779999999999999</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="C15" s="9">
         <f>C13*C11</f>
-        <v>30.986830000000001</v>
+        <v>30.321660000000001</v>
       </c>
       <c r="D15" s="9">
         <f>D13*D11</f>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C16" s="16">
         <f>C6*1000/C15</f>
-        <v>8.2551199977538854</v>
+        <v>8.2614210435708326</v>
       </c>
       <c r="D16" s="16">
         <f>D6*1000/D15</f>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="C17" s="9">
         <f>C5*1000/C16</f>
-        <v>36.401651348709926</v>
+        <v>36.071276167664678</v>
       </c>
       <c r="D17" s="9">
         <f>D5*1000/D16</f>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="C18" s="14">
         <f>C17/C10</f>
-        <v>0.9077718540825418</v>
+        <v>0.94675265531928288</v>
       </c>
       <c r="D18" s="14">
         <f>D17/D10</f>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="C19" s="13">
         <f>C17-C10</f>
-        <v>-3.6983486512900754</v>
+        <v>-2.0287238323353236</v>
       </c>
       <c r="D19" s="13">
         <f>D17-D10</f>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="C20" s="35">
         <f>C19/C10</f>
-        <v>-9.2228145917458232E-2</v>
+        <v>-5.3247344680717151E-2</v>
       </c>
       <c r="D20" s="35">
         <f>D19/D10</f>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C21" s="10">
         <f>C10*C16</f>
-        <v>331.03031190993079</v>
+        <v>314.76014176004873</v>
       </c>
       <c r="D21" s="10">
         <f>D10*D16</f>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="C22" s="11">
         <f>C11*C16</f>
-        <v>276.54651992475516</v>
+        <v>265.19161549862372</v>
       </c>
       <c r="D22" s="11">
         <f>D11*D16</f>

--- a/datos/2025-11-06-ejemplo-std-tecnico.xlsx
+++ b/datos/2025-11-06-ejemplo-std-tecnico.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="947" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2D2943E-0DF3-410E-AD41-3C5911498EB0}"/>
+  <xr:revisionPtr revIDLastSave="958" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89322A96-2EFD-4D10-80FE-1DDAA778226C}"/>
   <bookViews>
-    <workbookView xWindow="13215" yWindow="855" windowWidth="15390" windowHeight="14250" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
   <sheets>
     <sheet name="Estándar técnico" sheetId="21" r:id="rId1"/>
@@ -731,7 +731,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>ESM</t>
   </si>
@@ -845,6 +845,9 @@
   </si>
   <si>
     <t>4. Cálculos</t>
+  </si>
+  <si>
+    <t>Mozza</t>
   </si>
 </sst>
 </file>
@@ -3384,14 +3387,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
@@ -3410,8 +3413,11 @@
       <c r="F1" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="G1" s="15" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
@@ -3428,8 +3434,11 @@
       <c r="F2" s="18">
         <v>1</v>
       </c>
+      <c r="G2" s="18">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>34</v>
       </c>
@@ -3438,8 +3447,9 @@
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
       <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>32</v>
       </c>
@@ -3456,8 +3466,11 @@
       <c r="F4" s="2">
         <v>0.50470000000000004</v>
       </c>
+      <c r="G4" s="2">
+        <v>0.4</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
         <v>33</v>
       </c>
@@ -3474,8 +3487,11 @@
       <c r="F5" s="3">
         <v>0.20219999999999999</v>
       </c>
+      <c r="G5" s="3">
+        <v>0.18</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -3498,8 +3514,12 @@
         <f t="shared" si="0"/>
         <v>0.30250000000000005</v>
       </c>
+      <c r="G6" s="6">
+        <f>G4-G5</f>
+        <v>0.22000000000000003</v>
+      </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -3522,8 +3542,12 @@
         <f t="shared" si="1"/>
         <v>0.62083228879418395</v>
       </c>
+      <c r="G7" s="7">
+        <f>(1-G4)/(1-G5)</f>
+        <v>0.7317073170731706</v>
+      </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -3546,8 +3570,12 @@
         <f t="shared" si="2"/>
         <v>0.40063404002377645</v>
       </c>
+      <c r="G8" s="8">
+        <f>G5/G4</f>
+        <v>0.44999999999999996</v>
+      </c>
     </row>
-    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>35</v>
       </c>
@@ -3556,8 +3584,9 @@
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
         <v>17</v>
       </c>
@@ -3574,8 +3603,11 @@
       <c r="F10" s="27">
         <v>24.82</v>
       </c>
+      <c r="G10" s="27">
+        <v>38.1</v>
+      </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>18</v>
       </c>
@@ -3592,8 +3624,11 @@
       <c r="F11" s="29">
         <v>33.659999999999997</v>
       </c>
+      <c r="G11" s="29">
+        <v>32.1</v>
+      </c>
     </row>
-    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="30" t="s">
         <v>36</v>
       </c>
@@ -3602,8 +3637,9 @@
       <c r="D12" s="31"/>
       <c r="E12" s="31"/>
       <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
         <v>31</v>
       </c>
@@ -3620,8 +3656,11 @@
       <c r="F13" s="33">
         <v>0.97330000000000005</v>
       </c>
+      <c r="G13" s="33">
+        <v>0.9446</v>
+      </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>37</v>
       </c>
@@ -3630,8 +3669,9 @@
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
       <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -3654,8 +3694,12 @@
         <f>F13*F11</f>
         <v>32.761277999999997</v>
       </c>
+      <c r="G15" s="9">
+        <f>G13*G11</f>
+        <v>30.321660000000001</v>
+      </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>1</v>
       </c>
@@ -3678,8 +3722,12 @@
         <f>F6*1000/F15</f>
         <v>9.2334615273555585</v>
       </c>
+      <c r="G16" s="16">
+        <f>G6*1000/G15</f>
+        <v>7.2555394394634076</v>
+      </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -3702,8 +3750,12 @@
         <f>F5*1000/F16</f>
         <v>21.898612930909085</v>
       </c>
+      <c r="G17" s="9">
+        <f>G5*1000/G16</f>
+        <v>24.808630909090905</v>
+      </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
@@ -3726,8 +3778,12 @@
         <f t="shared" si="3"/>
         <v>0.88229705603985031</v>
       </c>
+      <c r="G18" s="14">
+        <f>G17/G10</f>
+        <v>0.65114516821760904</v>
+      </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>16</v>
       </c>
@@ -3750,8 +3806,12 @@
         <f t="shared" si="4"/>
         <v>-2.9213870690909154</v>
       </c>
+      <c r="G19" s="13">
+        <f>G17-G10</f>
+        <v>-13.291369090909097</v>
+      </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
@@ -3774,8 +3834,12 @@
         <f t="shared" si="5"/>
         <v>-0.11770294396014969</v>
       </c>
+      <c r="G20" s="35">
+        <f>G19/G10</f>
+        <v>-0.34885483178239096</v>
+      </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
@@ -3798,8 +3862,12 @@
         <f t="shared" si="6"/>
         <v>229.17451510896495</v>
       </c>
+      <c r="G21" s="10">
+        <f>G10*G16</f>
+        <v>276.43605264355585</v>
+      </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>11</v>
       </c>
@@ -3821,6 +3889,10 @@
       <c r="F22" s="11">
         <f t="shared" si="7"/>
         <v>310.79831501078809</v>
+      </c>
+      <c r="G22" s="11">
+        <f>G11*G16</f>
+        <v>232.9028160067754</v>
       </c>
     </row>
   </sheetData>

--- a/datos/2025-11-06-ejemplo-std-tecnico.xlsx
+++ b/datos/2025-11-06-ejemplo-std-tecnico.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="958" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89322A96-2EFD-4D10-80FE-1DDAA778226C}"/>
+  <xr:revisionPtr revIDLastSave="959" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D9DDED1-E90C-4CC9-8D4B-8C486BDEE985}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
@@ -712,7 +712,7 @@
     <definedName name="zzzzzzzzzzzzzzzzzz" localSheetId="0" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
     <definedName name="zzzzzzzzzzzzzzzzzz" hidden="1">{"QQQ",#N/A,FALSE,"RIEP"}</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -724,6 +724,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -733,134 +735,134 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
+    <t>Estándar de producto</t>
+  </si>
+  <si>
+    <t>Fórmulas</t>
+  </si>
+  <si>
+    <t>Vaca</t>
+  </si>
+  <si>
+    <t>Mezcla</t>
+  </si>
+  <si>
+    <t>Oveja</t>
+  </si>
+  <si>
+    <t>Bajo en MG</t>
+  </si>
+  <si>
+    <t>Mozza</t>
+  </si>
+  <si>
+    <t>Fabricación, KG</t>
+  </si>
+  <si>
+    <t>1. Características del queso</t>
+  </si>
+  <si>
+    <t>EST salida salado</t>
+  </si>
+  <si>
+    <t>MG salida salado</t>
+  </si>
+  <si>
     <t>ESM</t>
   </si>
   <si>
+    <t>=B4-B5</t>
+  </si>
+  <si>
+    <t>HFD</t>
+  </si>
+  <si>
+    <t>=(1-B4)/(1-B5)</t>
+  </si>
+  <si>
+    <t>G/ES</t>
+  </si>
+  <si>
+    <t>=B5/B4</t>
+  </si>
+  <si>
+    <t>2. Composición de la leche de fabricación</t>
+  </si>
+  <si>
+    <t>Leche en cuba MG (g/L)</t>
+  </si>
+  <si>
+    <t>Leche en cuba MP (g/L)</t>
+  </si>
+  <si>
+    <t>3. Datos tecnológicos</t>
+  </si>
+  <si>
+    <t>Recup MP (dato real de la fabricación)</t>
+  </si>
+  <si>
+    <t>4. Cálculos</t>
+  </si>
+  <si>
+    <t>ESM queso obtenido a partir de MP leche (g/L)</t>
+  </si>
+  <si>
+    <t>=B13*B11</t>
+  </si>
+  <si>
     <t>Litraje unitario</t>
   </si>
   <si>
+    <t>=B6*1000/B15</t>
+  </si>
+  <si>
     <t>MG teórica en la cuba (g/L)</t>
   </si>
   <si>
-    <t>Mezcla</t>
-  </si>
-  <si>
-    <t>Vaca</t>
-  </si>
-  <si>
-    <t>Oveja</t>
-  </si>
-  <si>
-    <t>Bajo en MG</t>
-  </si>
-  <si>
-    <t>Fabricación, KG</t>
-  </si>
-  <si>
-    <t>HFD</t>
-  </si>
-  <si>
-    <t>G/ES</t>
+    <t>=B5*1000/B16</t>
   </si>
   <si>
     <t>Recup MG</t>
   </si>
   <si>
+    <t>=B17/B10</t>
+  </si>
+  <si>
+    <t>MG pérdida bruta en suero (g/L)</t>
+  </si>
+  <si>
+    <t>=B17-B10</t>
+  </si>
+  <si>
+    <t>MG pérdida bruta en suero %</t>
+  </si>
+  <si>
+    <t>=B19/B10</t>
+  </si>
+  <si>
+    <t>Consumo MG/kg queso</t>
+  </si>
+  <si>
+    <t>=B10*B16</t>
+  </si>
+  <si>
     <t>Consumo MP/kg queso</t>
   </si>
   <si>
-    <t>MG pérdida bruta en suero %</t>
-  </si>
-  <si>
-    <t>Consumo MG/kg queso</t>
-  </si>
-  <si>
-    <t>Estándar de producto</t>
-  </si>
-  <si>
-    <t>ESM queso obtenido a partir de MP leche (g/L)</t>
-  </si>
-  <si>
-    <t>MG pérdida bruta en suero (g/L)</t>
-  </si>
-  <si>
-    <t>Leche en cuba MG (g/L)</t>
-  </si>
-  <si>
-    <t>Leche en cuba MP (g/L)</t>
-  </si>
-  <si>
-    <t>=B4-B5</t>
-  </si>
-  <si>
-    <t>=(1-B4)/(1-B5)</t>
-  </si>
-  <si>
-    <t>=B5/B4</t>
-  </si>
-  <si>
-    <t>Fórmulas</t>
-  </si>
-  <si>
-    <t>=B13*B11</t>
-  </si>
-  <si>
-    <t>=B6*1000/B15</t>
-  </si>
-  <si>
-    <t>=B5*1000/B16</t>
-  </si>
-  <si>
-    <t>=B17/B10</t>
-  </si>
-  <si>
-    <t>=B17-B10</t>
-  </si>
-  <si>
-    <t>=B19/B10</t>
-  </si>
-  <si>
-    <t>=B10*B16</t>
-  </si>
-  <si>
     <t>=B11*B16</t>
-  </si>
-  <si>
-    <t>Recup MP (dato real de la fabricación)</t>
-  </si>
-  <si>
-    <t>EST salida salado</t>
-  </si>
-  <si>
-    <t>MG salida salado</t>
-  </si>
-  <si>
-    <t>1. Características del queso</t>
-  </si>
-  <si>
-    <t>2. Composición de la leche de fabricación</t>
-  </si>
-  <si>
-    <t>3. Datos tecnológicos</t>
-  </si>
-  <si>
-    <t>4. Cálculos</t>
-  </si>
-  <si>
-    <t>Mozza</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="165" formatCode="#,##0.000_ ;[Red]\-#,##0.000\ "/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1088,7 +1090,9 @@
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{28C21CB3-7664-42D2-9D67-4CB284AD2D41}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1129,13 +1133,7 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>2010</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3" refreshError="1"/>
       <sheetData sheetId="4" refreshError="1"/>
@@ -1145,53 +1143,17 @@
       <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9" refreshError="1"/>
       <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11">
-        <row r="6">
-          <cell r="O6">
-            <v>29.297000000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12">
-        <row r="73">
-          <cell r="G73">
-            <v>1.54</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
       <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14">
-        <row r="258">
-          <cell r="F258">
-            <v>2.2000000000000002</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
-      <sheetData sheetId="16">
-        <row r="270">
-          <cell r="C270" t="str">
-            <v>E1</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="16"/>
       <sheetData sheetId="17" refreshError="1"/>
       <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19">
-        <row r="9">
-          <cell r="AD9">
-            <v>4.3841000000000001</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="19"/>
       <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21">
-        <row r="3">
-          <cell r="E3" t="str">
-            <v>JAN2010</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="21"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1248,444 +1210,15 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9" refreshError="1">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>January 2008</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>February 2008</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>March 2008</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>April 2008</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>May 2008</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>June 2008</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>July 2008</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>August 2008</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>September 2008</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>October 2008</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>November 2008</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>December 2008</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>January 2009</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>February 2009</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>March 2009</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>April 2009</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>May 2009</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>June 2009</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>July 2009</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>August 2009</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>September 2009</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>October 2009</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>November 2009</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>December 2009</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="9" refreshError="1"/>
       <sheetData sheetId="10"/>
-      <sheetData sheetId="11" refreshError="1">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>January 2008</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>February 2008</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>March 2008</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>April 2008</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>May 2008</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>June 2008</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>July 2008</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>August 2008</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>September 2008</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>October 2008</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>November 2008</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>December 2008</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>January 2009</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>February 2009</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>March 2009</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>April 2009</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>May 2009</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>June 2009</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>July 2009</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>August 2009</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>September 2009</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>October 2009</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>November 2009</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>December 2009</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="11" refreshError="1"/>
       <sheetData sheetId="12"/>
-      <sheetData sheetId="13" refreshError="1">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>January 2008</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>February 2008</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>March 2008</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>April 2008</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>May 2008</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>June 2008</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>July 2008</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>August 2008</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>September 2008</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>October 2008</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>November 2008</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>December 2008</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>January 2009</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>February 2009</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>March 2009</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>April 2009</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>May 2009</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>June 2009</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>July 2009</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>August 2009</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>September 2009</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>October 2009</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>November 2009</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>December 2009</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="13" refreshError="1"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
-      <sheetData sheetId="17" refreshError="1">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>December 2008</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>January 2009</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>February 2009</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>March 2009</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>April 2009</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>May 2009</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>June 2009</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>July 2009</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>August 2009</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>September 2009</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>October 2009</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>November 2009</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>December 2009</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="17" refreshError="1"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
@@ -1728,13 +1261,7 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>__Amount_for_Monthly_1</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
@@ -1818,917 +1345,7 @@
       <sheetName val="DATA"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
-        <row r="2">
-          <cell r="B2" t="str">
-            <v xml:space="preserve"> Stabilimento di</v>
-          </cell>
-          <cell r="H2" t="str">
-            <v>SCHEDA RILEVAZIONE TEMPI</v>
-          </cell>
-          <cell r="O2" t="str">
-            <v xml:space="preserve"> Data :</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v xml:space="preserve"> CERTOSA </v>
-          </cell>
-          <cell r="D3">
-            <v>220</v>
-          </cell>
-          <cell r="F3" t="str">
-            <v>Reparto :</v>
-          </cell>
-          <cell r="G3" t="str">
-            <v>FUSI</v>
-          </cell>
-          <cell r="H3">
-            <v>210</v>
-          </cell>
-          <cell r="I3" t="str">
-            <v>PREPARAZIONE IMPASTI E FUSIONE</v>
-          </cell>
-          <cell r="O3" t="str">
-            <v xml:space="preserve"> Gennaio 2004</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v xml:space="preserve"> PRODUZIONE :</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v xml:space="preserve">CREMA BEL PAESE  NORMALE + BIANCO + CREMOZOLA </v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="D5" t="str">
-            <v>+ FILANTE + FILANTE x PIZZA + IDEA PIZZA + FORMAGGIO PER PIZZA</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6" t="str">
-            <v>Persone</v>
-          </cell>
-          <cell r="G6" t="str">
-            <v>Tempo impiegato</v>
-          </cell>
-          <cell r="J6" t="str">
-            <v>Quantità</v>
-          </cell>
-          <cell r="L6" t="str">
-            <v>Tempo</v>
-          </cell>
-          <cell r="M6" t="str">
-            <v>Prodotti destinatari</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="D7" t="str">
-            <v>OPERAZIONI</v>
-          </cell>
-          <cell r="F7" t="str">
-            <v>occupate</v>
-          </cell>
-          <cell r="G7" t="str">
-            <v>Ore</v>
-          </cell>
-          <cell r="H7" t="str">
-            <v>Ore</v>
-          </cell>
-          <cell r="I7" t="str">
-            <v>Totale</v>
-          </cell>
-          <cell r="L7" t="str">
-            <v>in ore</v>
-          </cell>
-          <cell r="M7" t="str">
-            <v>C.B.P.</v>
-          </cell>
-          <cell r="N7" t="str">
-            <v>C.B.P +.</v>
-          </cell>
-          <cell r="P7" t="str">
-            <v>Filante</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="F8" t="str">
-            <v>Posizioni</v>
-          </cell>
-          <cell r="G8" t="str">
-            <v>squadra</v>
-          </cell>
-          <cell r="H8" t="str">
-            <v>squadra</v>
-          </cell>
-          <cell r="I8" t="str">
-            <v>ore ind</v>
-          </cell>
-          <cell r="J8" t="str">
-            <v>Kg</v>
-          </cell>
-          <cell r="K8" t="str">
-            <v>Kg</v>
-          </cell>
-          <cell r="L8" t="str">
-            <v>riferito a</v>
-          </cell>
-          <cell r="M8" t="str">
-            <v>Normale</v>
-          </cell>
-          <cell r="N8" t="str">
-            <v>Dolc. Crem.</v>
-          </cell>
-          <cell r="O8" t="str">
-            <v>K 1</v>
-          </cell>
-          <cell r="P8" t="str">
-            <v>Idea Pizza</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="F9" t="str">
-            <v>occupate</v>
-          </cell>
-          <cell r="G9" t="str">
-            <v>in '</v>
-          </cell>
-          <cell r="H9" t="str">
-            <v>decimali</v>
-          </cell>
-          <cell r="I9" t="str">
-            <v>decimali</v>
-          </cell>
-          <cell r="J9" t="str">
-            <v>settimana</v>
-          </cell>
-          <cell r="K9" t="str">
-            <v>giorno</v>
-          </cell>
-          <cell r="L9" t="str">
-            <v>100 Kg</v>
-          </cell>
-          <cell r="N9" t="str">
-            <v xml:space="preserve">4 F-Proc.-Tir. </v>
-          </cell>
-          <cell r="P9" t="str">
-            <v>Rapè - Mozz.</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="G11" t="str">
-            <v xml:space="preserve"> x C.B.P. Normale</v>
-          </cell>
-          <cell r="J11" t="str">
-            <v xml:space="preserve"> x C.B.P. +  e  Dolcelatte Cremoso</v>
-          </cell>
-          <cell r="M11" t="str">
-            <v xml:space="preserve">  x Filante + Idea Pizza + Filante Rapè</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="C12" t="str">
-            <v xml:space="preserve"> Determinazione gg./anno lavorati</v>
-          </cell>
-          <cell r="G12" t="str">
-            <v>gg/sett.</v>
-          </cell>
-          <cell r="H12" t="str">
-            <v>sett/anno</v>
-          </cell>
-          <cell r="I12" t="str">
-            <v>gg/anno</v>
-          </cell>
-          <cell r="J12" t="str">
-            <v>gg/sett.</v>
-          </cell>
-          <cell r="K12" t="str">
-            <v>sett/anno</v>
-          </cell>
-          <cell r="L12" t="str">
-            <v>gg/anno</v>
-          </cell>
-          <cell r="M12" t="str">
-            <v>gg/sett.</v>
-          </cell>
-          <cell r="N12" t="str">
-            <v>sett/anno</v>
-          </cell>
-          <cell r="O12" t="str">
-            <v>gg/anno</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="G15">
-            <v>5</v>
-          </cell>
-          <cell r="H15">
-            <v>50</v>
-          </cell>
-          <cell r="I15">
-            <v>250</v>
-          </cell>
-          <cell r="J15">
-            <v>5</v>
-          </cell>
-          <cell r="K15">
-            <v>50</v>
-          </cell>
-          <cell r="L15">
-            <v>250</v>
-          </cell>
-          <cell r="M15">
-            <v>5</v>
-          </cell>
-          <cell r="N15">
-            <v>50</v>
-          </cell>
-          <cell r="O15">
-            <v>250</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>A</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v xml:space="preserve"> OPERAZIONI PRELIMINARI</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="M17" t="str">
-            <v xml:space="preserve">Tempo in ore riferito a 100/kg </v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18">
-            <v>1</v>
-          </cell>
-          <cell r="C18" t="str">
-            <v xml:space="preserve"> Rifornimento materie prime a reparto :</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="C19" t="str">
-            <v xml:space="preserve"> - Scarico camions, pesatura palbox e stoccaggio in cella</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="C20" t="str">
-            <v xml:space="preserve"> - Prelievo campioni x analisi, controllo</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="C21" t="str">
-            <v xml:space="preserve">   rimanenze celle dinamica e formaggi</v>
-          </cell>
-          <cell r="F21">
-            <v>2</v>
-          </cell>
-          <cell r="G21">
-            <v>8</v>
-          </cell>
-          <cell r="H21">
-            <v>16</v>
-          </cell>
-          <cell r="I21">
-            <v>16</v>
-          </cell>
-          <cell r="K21">
-            <v>59868</v>
-          </cell>
-          <cell r="L21">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="M21">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="N21">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="O21">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="P21">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22">
-            <v>2</v>
-          </cell>
-          <cell r="C22" t="str">
-            <v xml:space="preserve"> Trasporto materie prime a reparto</v>
-          </cell>
-          <cell r="F22">
-            <v>2</v>
-          </cell>
-          <cell r="G22">
-            <v>8</v>
-          </cell>
-          <cell r="H22">
-            <v>8</v>
-          </cell>
-          <cell r="I22">
-            <v>16</v>
-          </cell>
-          <cell r="K22">
-            <v>59868</v>
-          </cell>
-          <cell r="L22">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="M22">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="N22">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="O22">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="P22">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23">
-            <v>3</v>
-          </cell>
-          <cell r="C23" t="str">
-            <v xml:space="preserve"> Lavaggio palbox m.p. + travaso da cartonbox altri</v>
-          </cell>
-          <cell r="F23">
-            <v>2</v>
-          </cell>
-          <cell r="G23">
-            <v>8</v>
-          </cell>
-          <cell r="H23">
-            <v>8</v>
-          </cell>
-          <cell r="I23">
-            <v>16</v>
-          </cell>
-          <cell r="K23">
-            <v>59868</v>
-          </cell>
-          <cell r="L23">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="M23">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="N23">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="O23">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-          <cell r="P23">
-            <v>2.6725462684572727E-2</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="C24" t="str">
-            <v xml:space="preserve"> Analisi materie prime</v>
-          </cell>
-          <cell r="G24">
-            <v>8</v>
-          </cell>
-          <cell r="H24">
-            <v>0</v>
-          </cell>
-          <cell r="I24">
-            <v>0</v>
-          </cell>
-          <cell r="K24">
-            <v>22660</v>
-          </cell>
-          <cell r="L24">
-            <v>0</v>
-          </cell>
-          <cell r="M24">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>B</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="C26" t="str">
-            <v xml:space="preserve"> PREPARAZIONI IMPASTI E FUSIONE</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27">
-            <v>1</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v xml:space="preserve"> Impostazione ricette + carico + analisi</v>
-          </cell>
-          <cell r="F27">
-            <v>2</v>
-          </cell>
-          <cell r="G27">
-            <v>8</v>
-          </cell>
-          <cell r="H27">
-            <v>8</v>
-          </cell>
-          <cell r="I27">
-            <v>16</v>
-          </cell>
-          <cell r="K27">
-            <v>22660</v>
-          </cell>
-          <cell r="L27">
-            <v>7.0609002647837593E-2</v>
-          </cell>
-          <cell r="M27">
-            <v>7.0609002647837593E-2</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29">
-            <v>2</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v xml:space="preserve"> Assistenza impianto sterilizzazione e cremificazione</v>
-          </cell>
-          <cell r="F29">
-            <v>2</v>
-          </cell>
-          <cell r="G29">
-            <v>8</v>
-          </cell>
-          <cell r="H29">
-            <v>8</v>
-          </cell>
-          <cell r="I29">
-            <v>16</v>
-          </cell>
-          <cell r="K29">
-            <v>22660</v>
-          </cell>
-          <cell r="L29">
-            <v>7.0609002647837593E-2</v>
-          </cell>
-          <cell r="M29">
-            <v>7.0609002647837593E-2</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="C30" t="str">
-            <v xml:space="preserve"> Stephan + preparazione e carico caseina</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31">
-            <v>3</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v xml:space="preserve"> Carico burro, fusione burro </v>
-          </cell>
-          <cell r="G31">
-            <v>0</v>
-          </cell>
-          <cell r="H31">
-            <v>0</v>
-          </cell>
-          <cell r="I31">
-            <v>0</v>
-          </cell>
-          <cell r="K31">
-            <v>22660</v>
-          </cell>
-          <cell r="L31">
-            <v>0</v>
-          </cell>
-          <cell r="M31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33">
-            <v>4</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v xml:space="preserve"> Assistenza e controllo cremificazione</v>
-          </cell>
-          <cell r="H33">
-            <v>0</v>
-          </cell>
-          <cell r="I33">
-            <v>0</v>
-          </cell>
-          <cell r="K33">
-            <v>22660</v>
-          </cell>
-          <cell r="L33">
-            <v>0</v>
-          </cell>
-          <cell r="M33">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34">
-            <v>5</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v xml:space="preserve"> Cottura in 1 Ks : addetti Stephan + pesatura sali di fusione</v>
-          </cell>
-          <cell r="H34">
-            <v>0</v>
-          </cell>
-          <cell r="I34">
-            <v>0</v>
-          </cell>
-          <cell r="K34">
-            <v>22660</v>
-          </cell>
-          <cell r="L34">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35">
-            <v>6</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v xml:space="preserve"> Pressatura porzioni fusi + filante</v>
-          </cell>
-          <cell r="H35">
-            <v>0</v>
-          </cell>
-          <cell r="I35">
-            <v>0</v>
-          </cell>
-          <cell r="K35">
-            <v>59868</v>
-          </cell>
-          <cell r="L35">
-            <v>0</v>
-          </cell>
-          <cell r="M35">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37">
-            <v>7</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v xml:space="preserve"> Preparazione e cottura form. prefuso settimanale</v>
-          </cell>
-          <cell r="H37">
-            <v>0</v>
-          </cell>
-          <cell r="I37">
-            <v>0</v>
-          </cell>
-          <cell r="K37">
-            <v>113300</v>
-          </cell>
-          <cell r="L37">
-            <v>0</v>
-          </cell>
-          <cell r="M37">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39">
-            <v>8</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v xml:space="preserve"> Colatura linee + trasporto pasta a Stephan</v>
-          </cell>
-          <cell r="F39">
-            <v>2</v>
-          </cell>
-          <cell r="G39">
-            <v>8</v>
-          </cell>
-          <cell r="H39">
-            <v>8</v>
-          </cell>
-          <cell r="I39">
-            <v>16</v>
-          </cell>
-          <cell r="K39">
-            <v>29528</v>
-          </cell>
-          <cell r="L39">
-            <v>5.4185857491194797E-2</v>
-          </cell>
-          <cell r="M39">
-            <v>5.4185857491194797E-2</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41">
-            <v>9</v>
-          </cell>
-          <cell r="C41" t="str">
-            <v xml:space="preserve"> Lavaggio iniziale e finale Stephan</v>
-          </cell>
-          <cell r="F41">
-            <v>1</v>
-          </cell>
-          <cell r="G41">
-            <v>8</v>
-          </cell>
-          <cell r="H41">
-            <v>8</v>
-          </cell>
-          <cell r="I41">
-            <v>8</v>
-          </cell>
-          <cell r="K41">
-            <v>22660</v>
-          </cell>
-          <cell r="L41">
-            <v>3.5304501323918797E-2</v>
-          </cell>
-          <cell r="M41">
-            <v>3.5304501323918797E-2</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43">
-            <v>10</v>
-          </cell>
-          <cell r="C43" t="str">
-            <v xml:space="preserve"> Lavaggio iniziale + finale Combinator e linee, preparazione</v>
-          </cell>
-          <cell r="G43">
-            <v>8</v>
-          </cell>
-          <cell r="H43">
-            <v>8</v>
-          </cell>
-          <cell r="I43">
-            <v>0</v>
-          </cell>
-          <cell r="K43">
-            <v>29528</v>
-          </cell>
-          <cell r="L43">
-            <v>0</v>
-          </cell>
-          <cell r="M43">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="C44" t="str">
-            <v xml:space="preserve"> macchine formatrici e lavaggio allibert</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46">
-            <v>11</v>
-          </cell>
-          <cell r="C46" t="str">
-            <v>Lavaggio ferri</v>
-          </cell>
-          <cell r="F46">
-            <v>1</v>
-          </cell>
-          <cell r="G46">
-            <v>8</v>
-          </cell>
-          <cell r="H46">
-            <v>8</v>
-          </cell>
-          <cell r="I46">
-            <v>8</v>
-          </cell>
-          <cell r="K46">
-            <v>29528</v>
-          </cell>
-          <cell r="L46">
-            <v>2.7092928745597399E-2</v>
-          </cell>
-          <cell r="M46">
-            <v>2.7092928745597399E-2</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48">
-            <v>12</v>
-          </cell>
-          <cell r="C48" t="str">
-            <v>Travaso pasta a fusione da cartonbox a palbox</v>
-          </cell>
-          <cell r="H48">
-            <v>0</v>
-          </cell>
-          <cell r="I48">
-            <v>0</v>
-          </cell>
-          <cell r="K48">
-            <v>29528</v>
-          </cell>
-          <cell r="L48">
-            <v>0</v>
-          </cell>
-          <cell r="M48">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="C49" t="str">
-            <v xml:space="preserve"> Addetti Ks x Dolc. Cr. / CBP +/ 4 Form. / Process./ Tiramisù</v>
-          </cell>
-          <cell r="F49">
-            <v>2</v>
-          </cell>
-          <cell r="G49">
-            <v>8</v>
-          </cell>
-          <cell r="H49">
-            <v>8</v>
-          </cell>
-          <cell r="I49">
-            <v>16</v>
-          </cell>
-          <cell r="K49">
-            <v>6868</v>
-          </cell>
-          <cell r="L49">
-            <v>0.23296447291788003</v>
-          </cell>
-          <cell r="N49">
-            <v>0.23296447291788003</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="C50" t="str">
-            <v xml:space="preserve"> Capi reparto (vedi scheda allegato 3)</v>
-          </cell>
-          <cell r="L50">
-            <v>1.2026458208057728E-2</v>
-          </cell>
-          <cell r="M50">
-            <v>1.2026458208057728E-2</v>
-          </cell>
-          <cell r="N50">
-            <v>1.2026458208057728E-2</v>
-          </cell>
-          <cell r="O50">
-            <v>1.2026458208057728E-2</v>
-          </cell>
-          <cell r="P50">
-            <v>1.2026458208057728E-2</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="C52" t="str">
-            <v>NB  tener conto di 1 x 8 ore Magor</v>
-          </cell>
-          <cell r="F52">
-            <v>1</v>
-          </cell>
-          <cell r="G52">
-            <v>8</v>
-          </cell>
-          <cell r="H52">
-            <v>8</v>
-          </cell>
-          <cell r="I52">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="C56" t="str">
-            <v xml:space="preserve"> TEMPO TOTALE</v>
-          </cell>
-          <cell r="E56" t="str">
-            <v>ORE/100 KG.</v>
-          </cell>
-          <cell r="I56">
-            <v>136</v>
-          </cell>
-          <cell r="L56">
-            <v>0.58296861203604211</v>
-          </cell>
-          <cell r="M56">
-            <v>0.35000413911816208</v>
-          </cell>
-          <cell r="N56">
-            <v>0.32516731917965591</v>
-          </cell>
-          <cell r="O56">
-            <v>9.2202846261775911E-2</v>
-          </cell>
-          <cell r="P56">
-            <v>9.2202846261775911E-2</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="C60" t="str">
-            <v xml:space="preserve"> Determinanti 2004</v>
-          </cell>
-          <cell r="F60" t="str">
-            <v>KG/ANNO</v>
-          </cell>
-          <cell r="G60" t="str">
-            <v>GG/ANNO</v>
-          </cell>
-          <cell r="H60" t="str">
-            <v>KG/GIORNO</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="C61" t="str">
-            <v xml:space="preserve"> C.B.P. Normale</v>
-          </cell>
-          <cell r="F61">
-            <v>5665000</v>
-          </cell>
-          <cell r="G61">
-            <v>250</v>
-          </cell>
-          <cell r="H61">
-            <v>22660</v>
-          </cell>
-          <cell r="K61" t="str">
-            <v xml:space="preserve"> SEGUE SU SCHEDE DI CONFEZIONAMENTO</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="C62" t="str">
-            <v xml:space="preserve"> C.B.P. +,  Dolcelatte cremoso, Crema 4 formaggi, Processato</v>
-          </cell>
-          <cell r="F62">
-            <v>1717000</v>
-          </cell>
-          <cell r="G62">
-            <v>250</v>
-          </cell>
-          <cell r="H62">
-            <v>6868</v>
-          </cell>
-          <cell r="K62" t="str">
-            <v xml:space="preserve"> - FUSI PORZIONI</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="H63" t="str">
-            <v/>
-          </cell>
-          <cell r="K63" t="str">
-            <v xml:space="preserve"> - FILANTE</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="C64" t="str">
-            <v xml:space="preserve"> Filante + Idea Pizza + Fil. Rapè + Filone Mozz.</v>
-          </cell>
-          <cell r="F64">
-            <v>7585000</v>
-          </cell>
-          <cell r="G64">
-            <v>250</v>
-          </cell>
-          <cell r="H64">
-            <v>30340</v>
-          </cell>
-          <cell r="K64" t="str">
-            <v xml:space="preserve"> - FILANTE x PIZZA</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="K65" t="str">
-            <v xml:space="preserve"> - IDEA PIZZA</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="K66" t="str">
-            <v xml:space="preserve"> - FORMAGGIO PER PIZZA</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="C68" t="str">
-            <v xml:space="preserve"> TOTALI</v>
-          </cell>
-          <cell r="F68">
-            <v>14967000</v>
-          </cell>
-          <cell r="G68">
-            <v>248</v>
-          </cell>
-          <cell r="H68">
-            <v>59868</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
@@ -2813,13 +1430,7 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>_Amount_for_Monthly</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
@@ -2881,18 +1492,7 @@
       <sheetData sheetId="7" refreshError="1"/>
       <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10">
-        <row r="2">
-          <cell r="AR2">
-            <v>0.83</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="AR3">
-            <v>1.27</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="10"/>
       <sheetData sheetId="11" refreshError="1"/>
       <sheetData sheetId="12" refreshError="1"/>
       <sheetData sheetId="13" refreshError="1"/>
@@ -2903,13 +1503,7 @@
       <sheetData sheetId="18" refreshError="1"/>
       <sheetData sheetId="19" refreshError="1"/>
       <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21">
-        <row r="6">
-          <cell r="H6">
-            <v>82589</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23" refreshError="1"/>
       <sheetData sheetId="24" refreshError="1"/>
@@ -2980,117 +1574,16 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2" refreshError="1">
-        <row r="3">
-          <cell r="B3">
-            <v>1</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>JANVIER</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>2</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>FÉVRIER</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>3</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>MARS</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>4</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>AVRIL</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>5</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>MAI</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>6</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>JUIN</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>7</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>JUILLET</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>8</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>AOÛT</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>9</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>SEPTEMBRE</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12">
-            <v>10</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>OCTOBRE</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>11</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>NOVEMBRE</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14">
-            <v>12</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>DÉCEMBRE</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3128,7 +1621,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3234,7 +1727,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3376,7 +1869,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3388,36 +1881,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="21">
       <c r="A1" s="5" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="15" t="s">
-        <v>38</v>
-      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
@@ -3438,9 +1931,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="18.75">
       <c r="A3" s="22" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -3449,9 +1942,9 @@
       <c r="F3" s="23"/>
       <c r="G3" s="23"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="20" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2">
@@ -3470,9 +1963,9 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="21" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3">
@@ -3491,12 +1984,12 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C6" s="6">
         <f>C4-C5</f>
@@ -3519,12 +2012,12 @@
         <v>0.22000000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C7" s="7">
         <f>(1-C4)/(1-C5)</f>
@@ -3547,12 +2040,12 @@
         <v>0.7317073170731706</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" s="8">
         <f>C5/C4</f>
@@ -3575,9 +2068,9 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="18.75">
       <c r="A9" s="24" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
@@ -3586,9 +2079,9 @@
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="27"/>
       <c r="C10" s="27">
@@ -3607,9 +2100,9 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="29">
@@ -3628,9 +2121,9 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="18.75">
       <c r="A12" s="30" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
@@ -3639,9 +2132,9 @@
       <c r="F12" s="31"/>
       <c r="G12" s="31"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="32" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B13" s="33"/>
       <c r="C13" s="33">
@@ -3660,9 +2153,9 @@
         <v>0.9446</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="18.75">
       <c r="A14" s="19" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -3671,12 +2164,12 @@
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" s="9">
         <f>C13*C11</f>
@@ -3699,12 +2192,12 @@
         <v>30.321660000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" s="16">
         <f>C6*1000/C15</f>
@@ -3727,12 +2220,12 @@
         <v>7.2555394394634076</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C17" s="9">
         <f>C5*1000/C16</f>
@@ -3755,12 +2248,12 @@
         <v>24.808630909090905</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C18" s="14">
         <f>C17/C10</f>
@@ -3783,12 +2276,12 @@
         <v>0.65114516821760904</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="12" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B19" s="42" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C19" s="13">
         <f>C17-C10</f>
@@ -3811,12 +2304,12 @@
         <v>-13.291369090909097</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20" s="35">
         <f>C19/C10</f>
@@ -3839,12 +2332,12 @@
         <v>-0.34885483178239096</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="12" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C21" s="10">
         <f>C10*C16</f>
@@ -3867,12 +2360,12 @@
         <v>276.43605264355585</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C22" s="11">
         <f>C11*C16</f>
